--- a/engine/borouge_study/BOROUGE_Valuation_Model_09082026_public.xlsx
+++ b/engine/borouge_study/BOROUGE_Valuation_Model_09082026_public.xlsx
@@ -2942,102 +2942,102 @@
     </row>
     <row r="6">
       <c r="A6" s="26" t="n">
-        <v>0.04484680827418632</v>
+        <v>0.0508701898195711</v>
       </c>
       <c r="B6" s="23" t="n">
-        <v>3.749843589614441</v>
+        <v>3.144227956279106</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>4.183155930830396</v>
+        <v>3.425480168870383</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>4.788891871042499</v>
+        <v>3.796299748193475</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>5.697367275109789</v>
+        <v>4.308619459734347</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>7.214445320758032</v>
+        <v>5.064139479754758</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="26" t="n">
-        <v>0.04984680827418633</v>
+        <v>0.05587018981957111</v>
       </c>
       <c r="B7" s="23" t="n">
-        <v>3.234236804984493</v>
+        <v>2.762087159533806</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>3.535780111410452</v>
+        <v>2.965804072589653</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>3.936752484538973</v>
+        <v>3.22501899416255</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>4.497179179287316</v>
+        <v>3.566698720784074</v>
       </c>
       <c r="F7" s="23" t="n">
-        <v>5.337574022929579</v>
+        <v>4.038657825302612</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="26" t="n">
-        <v>0.05484680827418632</v>
+        <v>0.0608701898195711</v>
       </c>
       <c r="B8" s="23" t="n">
-        <v>2.83338406848312</v>
+        <v>2.454883571930389</v>
       </c>
       <c r="C8" s="23" t="n">
-        <v>3.050526689877888</v>
+        <v>2.606053224782932</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>3.328643488050918</v>
+        <v>2.793100756822747</v>
       </c>
       <c r="E8" s="23" t="n">
-        <v>3.698378029418823</v>
+        <v>3.031029383547609</v>
       </c>
       <c r="F8" s="23" t="n">
-        <v>4.215039878604873</v>
+        <v>3.344562516920206</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="26" t="n">
-        <v>0.05984680827418632</v>
+        <v>0.0658701898195711</v>
       </c>
       <c r="B9" s="23" t="n">
-        <v>2.51275966997218</v>
+        <v>2.202503464454367</v>
       </c>
       <c r="C9" s="23" t="n">
-        <v>2.673180065987575</v>
+        <v>2.316771104314995</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>2.872715859395584</v>
+        <v>2.454983916629508</v>
       </c>
       <c r="E9" s="23" t="n">
-        <v>3.128204487825287</v>
+        <v>2.625930154850942</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>3.467765960545859</v>
+        <v>2.843298104184189</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="26" t="n">
-        <v>0.06484680827418632</v>
+        <v>0.07087018981957111</v>
       </c>
       <c r="B10" s="23" t="n">
-        <v>2.250427556977055</v>
+        <v>1.9914416549302</v>
       </c>
       <c r="C10" s="23" t="n">
-        <v>2.371277201823014</v>
+        <v>2.079045543477089</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>2.518081343395401</v>
+        <v>2.183019664682139</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>2.700610336404119</v>
+        <v>2.308717244482246</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>2.934242139350521</v>
+        <v>2.464111132535419</v>
       </c>
     </row>
     <row r="12">
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="B14" s="23" t="n">
-        <v>2.1627835447656</v>
+        <v>1.796972468385304</v>
       </c>
       <c r="C14" s="23" t="n">
-        <v>2.181377475722164</v>
+        <v>1.816830305717374</v>
       </c>
     </row>
     <row r="15">
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="B15" s="23" t="n">
-        <v>2.74571351640826</v>
+        <v>2.295036612604027</v>
       </c>
       <c r="C15" s="23" t="n">
-        <v>2.752686594027506</v>
+        <v>2.304287206765658</v>
       </c>
     </row>
     <row r="16">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="B16" s="23" t="n">
-        <v>3.328643488050918</v>
+        <v>2.793100756822747</v>
       </c>
       <c r="C16" s="23" t="n">
-        <v>3.323995712332845</v>
+        <v>2.79174410781394</v>
       </c>
     </row>
     <row r="17">
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="B17" s="23" t="n">
-        <v>3.911573459693579</v>
+        <v>3.291164901041471</v>
       </c>
       <c r="C17" s="23" t="n">
-        <v>3.895304830638187</v>
+        <v>3.279201008862226</v>
       </c>
     </row>
     <row r="18">
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="B18" s="23" t="n">
-        <v>4.49450343133624</v>
+        <v>3.789229045260195</v>
       </c>
       <c r="C18" s="23" t="n">
-        <v>4.466613948943528</v>
+        <v>3.766657909910509</v>
       </c>
     </row>
     <row r="20">
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="B22" s="23" t="n">
-        <v>2.692103274909431</v>
+        <v>2.248692663596503</v>
       </c>
       <c r="C22" s="23" t="n">
-        <v>2.673054932267894</v>
+        <v>2.233868743063614</v>
       </c>
     </row>
     <row r="23">
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="B23" s="23" t="n">
-        <v>3.010373381480176</v>
+        <v>2.520896710209626</v>
       </c>
       <c r="C23" s="23" t="n">
-        <v>2.998525322300371</v>
+        <v>2.512806425438778</v>
       </c>
     </row>
     <row r="24">
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="B24" s="23" t="n">
-        <v>3.328643488050918</v>
+        <v>2.793100756822747</v>
       </c>
       <c r="C24" s="23" t="n">
-        <v>3.323995712332845</v>
+        <v>2.79174410781394</v>
       </c>
     </row>
     <row r="25">
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="B25" s="23" t="n">
-        <v>3.646913594621661</v>
+        <v>3.065304803435871</v>
       </c>
       <c r="C25" s="23" t="n">
-        <v>3.649466102365321</v>
+        <v>3.070681790189105</v>
       </c>
     </row>
     <row r="26">
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="B26" s="23" t="n">
-        <v>3.965183701192406</v>
+        <v>3.337508850048993</v>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.974936492397797</v>
+        <v>3.349619472564268</v>
       </c>
     </row>
     <row r="28">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>R-squared 0.088 on 216 weekly observations — statistically weak</t>
+          <t>R-squared 0.094 on 215 weekly observations — statistically weak</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
         </is>
       </c>
       <c r="B15" s="27" t="n">
-        <v>0.2709846257193927</v>
+        <v>0.4152894017177773</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         </is>
       </c>
       <c r="B68" s="17">
-        <f>B33+2969.8298269315565</f>
+        <f>B33+2504.9806793283</f>
         <v/>
       </c>
       <c r="C68" s="17">
@@ -9576,7 +9576,7 @@
         </is>
       </c>
       <c r="B70" s="17">
-        <f>B64+3043.0974106183016</f>
+        <f>B64+2566.7801399883047</f>
         <v/>
       </c>
       <c r="C70" s="17">

--- a/engine/borouge_study/BOROUGE_Valuation_Model_09082026_public.xlsx
+++ b/engine/borouge_study/BOROUGE_Valuation_Model_09082026_public.xlsx
@@ -1252,23 +1252,23 @@
         <v/>
       </c>
       <c r="E6" s="18">
-        <f>'Income Statement'!E5*Assumptions!$B$37/365</f>
+        <f>'Income Statement'!E5*Assumptions!$B$38/365</f>
         <v/>
       </c>
       <c r="F6" s="18">
-        <f>'Income Statement'!F5*Assumptions!$B$37/365</f>
+        <f>'Income Statement'!F5*Assumptions!$B$38/365</f>
         <v/>
       </c>
       <c r="G6" s="18">
-        <f>'Income Statement'!G5*Assumptions!$B$37/365</f>
+        <f>'Income Statement'!G5*Assumptions!$B$38/365</f>
         <v/>
       </c>
       <c r="H6" s="18">
-        <f>'Income Statement'!H5*Assumptions!$B$37/365</f>
+        <f>'Income Statement'!H5*Assumptions!$B$38/365</f>
         <v/>
       </c>
       <c r="I6" s="18">
-        <f>'Income Statement'!I5*Assumptions!$B$37/365</f>
+        <f>'Income Statement'!I5*Assumptions!$B$38/365</f>
         <v/>
       </c>
     </row>
@@ -1288,23 +1288,23 @@
         <v>523.702</v>
       </c>
       <c r="E7" s="18">
-        <f>('DCF'!B7+'DCF'!B8)*Assumptions!$B$38/365</f>
+        <f>('DCF'!B7+'DCF'!B8)*Assumptions!$B$39/365</f>
         <v/>
       </c>
       <c r="F7" s="18">
-        <f>('DCF'!C7+'DCF'!C8)*Assumptions!$B$38/365</f>
+        <f>('DCF'!C7+'DCF'!C8)*Assumptions!$B$39/365</f>
         <v/>
       </c>
       <c r="G7" s="18">
-        <f>('DCF'!D7+'DCF'!D8)*Assumptions!$B$38/365</f>
+        <f>('DCF'!D7+'DCF'!D8)*Assumptions!$B$39/365</f>
         <v/>
       </c>
       <c r="H7" s="18">
-        <f>('DCF'!E7+'DCF'!E8)*Assumptions!$B$38/365</f>
+        <f>('DCF'!E7+'DCF'!E8)*Assumptions!$B$39/365</f>
         <v/>
       </c>
       <c r="I7" s="18">
-        <f>('DCF'!F7+'DCF'!F8)*Assumptions!$B$38/365</f>
+        <f>('DCF'!F7+'DCF'!F8)*Assumptions!$B$39/365</f>
         <v/>
       </c>
     </row>
@@ -1399,23 +1399,23 @@
         <v/>
       </c>
       <c r="E10" s="18">
-        <f>('DCF'!B7+'DCF'!B8)*Assumptions!$B$39/365</f>
+        <f>('DCF'!B7+'DCF'!B8)*Assumptions!$B$40/365</f>
         <v/>
       </c>
       <c r="F10" s="18">
-        <f>('DCF'!C7+'DCF'!C8)*Assumptions!$B$39/365</f>
+        <f>('DCF'!C7+'DCF'!C8)*Assumptions!$B$40/365</f>
         <v/>
       </c>
       <c r="G10" s="18">
-        <f>('DCF'!D7+'DCF'!D8)*Assumptions!$B$39/365</f>
+        <f>('DCF'!D7+'DCF'!D8)*Assumptions!$B$40/365</f>
         <v/>
       </c>
       <c r="H10" s="18">
-        <f>('DCF'!E7+'DCF'!E8)*Assumptions!$B$39/365</f>
+        <f>('DCF'!E7+'DCF'!E8)*Assumptions!$B$40/365</f>
         <v/>
       </c>
       <c r="I10" s="18">
-        <f>('DCF'!F7+'DCF'!F8)*Assumptions!$B$39/365</f>
+        <f>('DCF'!F7+'DCF'!F8)*Assumptions!$B$40/365</f>
         <v/>
       </c>
     </row>
@@ -1549,23 +1549,23 @@
         <v/>
       </c>
       <c r="E14" s="32">
-        <f>D14-('DCF'!B20-Assumptions!$B$48*Assumptions!$B$18*(1-Assumptions!$B$19))+0.044111640571817566*Assumptions!$B$7</f>
+        <f>D14-('DCF'!B20-Assumptions!$B$53*Assumptions!$B$18*(1-Assumptions!$B$19))+0.044111640571817566*Assumptions!$B$7</f>
         <v/>
       </c>
       <c r="F14" s="32">
-        <f>E14-('DCF'!C20-Assumptions!$B$48*Assumptions!$B$18*(1-Assumptions!$B$19))+0.044111640571817566*Assumptions!$B$7</f>
+        <f>E14-('DCF'!C20-Assumptions!$B$53*Assumptions!$B$18*(1-Assumptions!$B$19))+0.044111640571817566*Assumptions!$B$7</f>
         <v/>
       </c>
       <c r="G14" s="32">
-        <f>F14-('DCF'!D20-Assumptions!$B$48*Assumptions!$B$18*(1-Assumptions!$B$19))+0.044111640571817566*Assumptions!$B$7</f>
+        <f>F14-('DCF'!D20-Assumptions!$B$53*Assumptions!$B$18*(1-Assumptions!$B$19))+0.044111640571817566*Assumptions!$B$7</f>
         <v/>
       </c>
       <c r="H14" s="32">
-        <f>G14-('DCF'!E20-Assumptions!$B$48*Assumptions!$B$18*(1-Assumptions!$B$19))+0.044111640571817566*Assumptions!$B$7</f>
+        <f>G14-('DCF'!E20-Assumptions!$B$53*Assumptions!$B$18*(1-Assumptions!$B$19))+0.044111640571817566*Assumptions!$B$7</f>
         <v/>
       </c>
       <c r="I14" s="32">
-        <f>H14-('DCF'!F20-Assumptions!$B$48*Assumptions!$B$18*(1-Assumptions!$B$19))+0.044111640571817566*Assumptions!$B$7</f>
+        <f>H14-('DCF'!F20-Assumptions!$B$53*Assumptions!$B$18*(1-Assumptions!$B$19))+0.044111640571817566*Assumptions!$B$7</f>
         <v/>
       </c>
     </row>
@@ -1740,17 +1740,14 @@
           <t>Less: tax on operating profit</t>
         </is>
       </c>
-      <c r="B7" s="17">
-        <f>B5*0+400.333</f>
-        <v/>
-      </c>
-      <c r="C7" s="17">
-        <f>C5*0+506.361</f>
-        <v/>
-      </c>
-      <c r="D7" s="17">
-        <f>D5*0+440.714</f>
-        <v/>
+      <c r="B7" s="25" t="n">
+        <v>400.333</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>506.361</v>
+      </c>
+      <c r="D7" s="25" t="n">
+        <v>440.714</v>
       </c>
       <c r="E7" s="17">
         <f>'DCF'!B15*Assumptions!$B$19</f>
@@ -1891,23 +1888,23 @@
         </is>
       </c>
       <c r="E11" s="30">
-        <f>Assumptions!$B$48*Assumptions!$B$18*(1-Assumptions!$B$19)</f>
+        <f>Assumptions!$B$53*Assumptions!$B$18*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
       <c r="F11" s="30">
-        <f>Assumptions!$B$48*Assumptions!$B$18*(1-Assumptions!$B$19)</f>
+        <f>Assumptions!$B$53*Assumptions!$B$18*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>Assumptions!$B$48*Assumptions!$B$18*(1-Assumptions!$B$19)</f>
+        <f>Assumptions!$B$53*Assumptions!$B$18*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
       <c r="H11" s="30">
-        <f>Assumptions!$B$48*Assumptions!$B$18*(1-Assumptions!$B$19)</f>
+        <f>Assumptions!$B$53*Assumptions!$B$18*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
       <c r="I11" s="30">
-        <f>Assumptions!$B$48*Assumptions!$B$18*(1-Assumptions!$B$19)</f>
+        <f>Assumptions!$B$53*Assumptions!$B$18*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
     </row>
@@ -2945,19 +2942,19 @@
         <v>0.0508701898195711</v>
       </c>
       <c r="B6" s="23" t="n">
-        <v>3.144227956279106</v>
+        <v>2.893894044153059</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>3.425480168870383</v>
+        <v>3.136632969508269</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>3.796299748193475</v>
+        <v>3.456448615077962</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>4.308619459734347</v>
+        <v>3.898031445496553</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>5.064139479754758</v>
+        <v>4.548899005574333</v>
       </c>
     </row>
     <row r="7">
@@ -2965,19 +2962,19 @@
         <v>0.05587018981957111</v>
       </c>
       <c r="B7" s="23" t="n">
-        <v>2.762087159533806</v>
+        <v>2.544997614368152</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>2.965804072589653</v>
+        <v>2.719048021800045</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>3.22501899416255</v>
+        <v>2.940313511870105</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>3.566698720784074</v>
+        <v>3.231736160532899</v>
       </c>
       <c r="F7" s="23" t="n">
-        <v>4.038657825302612</v>
+        <v>3.633994346502716</v>
       </c>
     </row>
     <row r="8">
@@ -2985,19 +2982,19 @@
         <v>0.0608701898195711</v>
       </c>
       <c r="B8" s="23" t="n">
-        <v>2.454883571930389</v>
+        <v>2.264351045241041</v>
       </c>
       <c r="C8" s="23" t="n">
-        <v>2.606053224782932</v>
+        <v>2.392041742172137</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>2.793100756822747</v>
+        <v>2.549854919607749</v>
       </c>
       <c r="E8" s="23" t="n">
-        <v>3.031029383547609</v>
+        <v>2.750387031869435</v>
       </c>
       <c r="F8" s="23" t="n">
-        <v>3.344562516920206</v>
+        <v>3.014395451235635</v>
       </c>
     </row>
     <row r="9">
@@ -3005,19 +3002,19 @@
         <v>0.0658701898195711</v>
       </c>
       <c r="B9" s="23" t="n">
-        <v>2.202503464454367</v>
+        <v>2.033640537639993</v>
       </c>
       <c r="C9" s="23" t="n">
-        <v>2.316771104314995</v>
+        <v>2.128918623131629</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>2.454983916629508</v>
+        <v>2.243992778539845</v>
       </c>
       <c r="E9" s="23" t="n">
-        <v>2.625930154850942</v>
+        <v>2.386128471680169</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>2.843298104184189</v>
+        <v>2.566642148549217</v>
       </c>
     </row>
     <row r="10">
@@ -3025,19 +3022,19 @@
         <v>0.07087018981957111</v>
       </c>
       <c r="B10" s="23" t="n">
-        <v>1.9914416549302</v>
+        <v>1.840569286563959</v>
       </c>
       <c r="C10" s="23" t="n">
-        <v>2.079045543477089</v>
+        <v>1.912538974720122</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>2.183019664682139</v>
+        <v>1.997797390198996</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>2.308717244482246</v>
+        <v>2.100690076601443</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>2.464111132535419</v>
+        <v>2.22768908764244</v>
       </c>
     </row>
     <row r="12">
@@ -3080,10 +3077,10 @@
         </is>
       </c>
       <c r="B14" s="23" t="n">
-        <v>1.796972468385304</v>
+        <v>1.61065079748036</v>
       </c>
       <c r="C14" s="23" t="n">
-        <v>1.816830305717374</v>
+        <v>1.425572526617797</v>
       </c>
     </row>
     <row r="15">
@@ -3093,10 +3090,10 @@
         </is>
       </c>
       <c r="B15" s="23" t="n">
-        <v>2.295036612604027</v>
+        <v>2.080252858544056</v>
       </c>
       <c r="C15" s="23" t="n">
-        <v>2.304287206765658</v>
+        <v>1.886828798766677</v>
       </c>
     </row>
     <row r="16">
@@ -3106,10 +3103,10 @@
         </is>
       </c>
       <c r="B16" s="23" t="n">
-        <v>2.793100756822747</v>
+        <v>2.549854919607749</v>
       </c>
       <c r="C16" s="23" t="n">
-        <v>2.79174410781394</v>
+        <v>2.348085070915562</v>
       </c>
     </row>
     <row r="17">
@@ -3119,10 +3116,10 @@
         </is>
       </c>
       <c r="B17" s="23" t="n">
-        <v>3.291164901041471</v>
+        <v>3.019456980671444</v>
       </c>
       <c r="C17" s="23" t="n">
-        <v>3.279201008862226</v>
+        <v>2.809341343064444</v>
       </c>
     </row>
     <row r="18">
@@ -3132,10 +3129,10 @@
         </is>
       </c>
       <c r="B18" s="23" t="n">
-        <v>3.789229045260195</v>
+        <v>3.48905904173514</v>
       </c>
       <c r="C18" s="23" t="n">
-        <v>3.766657909910509</v>
+        <v>3.270597615213326</v>
       </c>
     </row>
     <row r="20">
@@ -3178,10 +3175,10 @@
         </is>
       </c>
       <c r="B22" s="23" t="n">
-        <v>2.248692663596503</v>
+        <v>2.026691391607796</v>
       </c>
       <c r="C22" s="23" t="n">
-        <v>2.233868743063614</v>
+        <v>1.836039314234161</v>
       </c>
     </row>
     <row r="23">
@@ -3191,10 +3188,10 @@
         </is>
       </c>
       <c r="B23" s="23" t="n">
-        <v>2.520896710209626</v>
+        <v>2.288273155607775</v>
       </c>
       <c r="C23" s="23" t="n">
-        <v>2.512806425438778</v>
+        <v>2.09206219257486</v>
       </c>
     </row>
     <row r="24">
@@ -3204,10 +3201,10 @@
         </is>
       </c>
       <c r="B24" s="23" t="n">
-        <v>2.793100756822747</v>
+        <v>2.549854919607749</v>
       </c>
       <c r="C24" s="23" t="n">
-        <v>2.79174410781394</v>
+        <v>2.348085070915562</v>
       </c>
     </row>
     <row r="25">
@@ -3217,10 +3214,10 @@
         </is>
       </c>
       <c r="B25" s="23" t="n">
-        <v>3.065304803435871</v>
+        <v>2.811436683607727</v>
       </c>
       <c r="C25" s="23" t="n">
-        <v>3.070681790189105</v>
+        <v>2.604107949256261</v>
       </c>
     </row>
     <row r="26">
@@ -3230,10 +3227,10 @@
         </is>
       </c>
       <c r="B26" s="23" t="n">
-        <v>3.337508850048993</v>
+        <v>3.073018447607703</v>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.349619472564268</v>
+        <v>2.86013082759696</v>
       </c>
     </row>
     <row r="28">
@@ -4522,7 +4519,7 @@
         </is>
       </c>
       <c r="B24" s="12">
-        <f>Assumptions!$B$46</f>
+        <f>Assumptions!$B$51</f>
         <v/>
       </c>
     </row>
@@ -4937,7 +4934,7 @@
         </is>
       </c>
       <c r="B26" s="18">
-        <f>Assumptions!$B$48</f>
+        <f>Assumptions!$B$53</f>
         <v/>
       </c>
     </row>
@@ -5055,7 +5052,7 @@
         </is>
       </c>
       <c r="B36" s="19">
-        <f>3725.9970000000003/Assumptions!$B$7</f>
+        <f>Assumptions!$B$44/Assumptions!$B$7</f>
         <v/>
       </c>
     </row>
@@ -5066,7 +5063,7 @@
         </is>
       </c>
       <c r="B37" s="11">
-        <f>AVERAGE(0.2186715799422921,0.27455707565286336,0.26637758783031906)</f>
+        <f>AVERAGE(Assumptions!$B$45,Assumptions!$B$46,Assumptions!$B$47)</f>
         <v/>
       </c>
     </row>
@@ -5077,11 +5074,11 @@
         </is>
       </c>
       <c r="B38" s="20">
-        <f>(B37-Assumptions!$B$46)/(C22-Assumptions!$B$46)</f>
+        <f>(B37-Assumptions!$B$51)/(C22-Assumptions!$B$51)</f>
         <v/>
       </c>
       <c r="C38" s="20">
-        <f>(B37-Assumptions!$B$46)/(B22-Assumptions!$B$46)</f>
+        <f>(B37-Assumptions!$B$51)/(B22-Assumptions!$B$51)</f>
         <v/>
       </c>
     </row>
@@ -5107,11 +5104,11 @@
         </is>
       </c>
       <c r="B40" s="8">
-        <f>'Relative &amp; Normalized'!$B$46</f>
+        <f>'Relative &amp; Normalized'!$B$48</f>
         <v/>
       </c>
       <c r="C40" s="8">
-        <f>'Relative &amp; Normalized'!$B$45</f>
+        <f>'Relative &amp; Normalized'!$B$47</f>
         <v/>
       </c>
     </row>
@@ -5122,11 +5119,11 @@
         </is>
       </c>
       <c r="B41" s="8">
-        <f>'Relative &amp; Normalized'!$B$21</f>
+        <f>'Relative &amp; Normalized'!$B$23</f>
         <v/>
       </c>
       <c r="C41" s="8">
-        <f>'Relative &amp; Normalized'!$B$21</f>
+        <f>'Relative &amp; Normalized'!$B$23</f>
         <v/>
       </c>
     </row>
@@ -5153,7 +5150,7 @@
         </is>
       </c>
       <c r="B44" s="22">
-        <f>MIN(B34,B35,B39,B40,B41,C34,C35,C39,C40,C41)</f>
+        <f>MIN(B34,B35,B39,B40,B41,C34,C35,C39,C40)</f>
         <v/>
       </c>
     </row>
@@ -5164,7 +5161,7 @@
         </is>
       </c>
       <c r="B45" s="21">
-        <f>MEDIAN(B34,B35,B39,B40,B41,C34,C35,C39,C40,C41)</f>
+        <f>MEDIAN(B34,B35,B39,B40,B41,C34,C35,C39,C40)</f>
         <v/>
       </c>
     </row>
@@ -5175,7 +5172,7 @@
         </is>
       </c>
       <c r="B46" s="22">
-        <f>MAX(B34,B35,B39,B40,B41,C34,C35,C39,C40,C41)</f>
+        <f>MAX(B34,B35,B39,B40,B41,C34,C35,C39,C40)</f>
         <v/>
       </c>
     </row>
@@ -5215,7 +5212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -5420,11 +5417,11 @@
         </is>
       </c>
       <c r="B16" s="27" t="n">
-        <v>1.0021</v>
+        <v>0.9101</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>global chemicals, corrected for cash</t>
+          <t>Chemical (Diversified) — the SAME industry row the EV/EBITDA anchor uses</t>
         </is>
       </c>
     </row>
@@ -5522,26 +5519,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Realisation residual — polyethylene</t>
+          <t>Sales over production (partner sourcing)</t>
         </is>
       </c>
       <c r="B24" s="24" t="n">
-        <v>1.067577742993017</v>
+        <v>1.029563262699265</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>three-year mean; computed on Segments</t>
+          <t>sales exceed production because Borouge sources from partners — measured from the audited record and held flat</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Realisation residual — polypropylene</t>
+          <t>Realisation residual — polyethylene</t>
         </is>
       </c>
       <c r="B25" s="24" t="n">
-        <v>1.032106492774941</v>
+        <v>1.067577742993017</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -5552,132 +5549,132 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Other production cost — fixed leg</t>
-        </is>
-      </c>
-      <c r="B26" s="25" t="n">
-        <v>663.0482068711129</v>
+          <t>Realisation residual — polypropylene</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>1.032106492774941</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>PASTED CLASS 2: least squares across three audited years</t>
+          <t>three-year mean; computed on Segments</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Other production cost — per tonne of production</t>
-        </is>
-      </c>
-      <c r="B27" s="24" t="n">
-        <v>0.2006348493835886</v>
+          <t>Other production cost — fixed leg</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="n">
+        <v>789.7908363659598</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>PASTED CLASS 2: USD million per kt, same regression</t>
+          <t>PASTED CLASS 2: least squares across three audited years</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Feedstock cost per tonne, FY2025 actual</t>
-        </is>
-      </c>
-      <c r="B28" s="29" t="n">
-        <v>256.1819980217606</v>
+          <t>Other production cost — per tonne of production</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>0.2006348493835886</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>USD per tonne produced — the base both legs escalate from</t>
+          <t>PASTED CLASS 2: USD million per kt, same regression</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Polypropylene benchmark, FY2025 actual</t>
-        </is>
-      </c>
-      <c r="B29" s="25" t="n">
-        <v>851</v>
+          <t>Feedstock cost per tonne, FY2025 actual</t>
+        </is>
+      </c>
+      <c r="B29" s="29" t="n">
+        <v>256.1819980217606</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>the traded leg escalates on THIS, not on consumer inflation</t>
+          <t>USD per tonne produced — the base both legs escalate from</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Contracted ethane real escalation</t>
-        </is>
-      </c>
-      <c r="B30" s="26" t="n">
-        <v>0</v>
+          <t>Polypropylene benchmark, FY2025 actual</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="n">
+        <v>851</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>zero: the pricing formula is not disclosed, so none is invented</t>
+          <t>the traded leg escalates on THIS, not on consumer inflation</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Contracted ethane real escalation</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>zero: the pricing formula is not disclosed, so none is invented</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>UAE consumer inflation</t>
         </is>
       </c>
-      <c r="B31" s="26" t="n">
+      <c r="B32" s="26" t="n">
         <v>0.021</v>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>escalates the DOMESTIC fixed cost leg only</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>FIXED COSTS, WORKING CAPITAL AND CAPITAL SPEND</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>General and administrative, FY2025 excluding depreciation</t>
-        </is>
-      </c>
-      <c r="B34" s="29" t="n">
-        <v>188</v>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>USD million</t>
-        </is>
-      </c>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Other income, FY2025</t>
+          <t>General and administrative, FY2025 excluding depreciation</t>
         </is>
       </c>
       <c r="B35" s="29" t="n">
-        <v>26.321</v>
+        <v>188</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -5688,56 +5685,56 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Other revenue, FY2025</t>
+          <t>Other income, FY2025</t>
         </is>
       </c>
       <c r="B36" s="29" t="n">
-        <v>44</v>
+        <v>26.321</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>USD million, run off at 10% a year</t>
+          <t>USD million</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Days sales outstanding</t>
+          <t>Other revenue, FY2025</t>
         </is>
       </c>
       <c r="B37" s="29" t="n">
-        <v>50.89129017431239</v>
+        <v>44</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>days, from the audited statements</t>
+          <t>USD million, run off at 10% a year</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Days inventory</t>
+          <t>Days sales outstanding</t>
         </is>
       </c>
       <c r="B38" s="29" t="n">
-        <v>61.83088660781963</v>
+        <v>50.89129017431239</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>days, from the audited statements</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Days payable</t>
+          <t>Days inventory</t>
         </is>
       </c>
       <c r="B39" s="29" t="n">
-        <v>92.49608922133605</v>
+        <v>61.83088660781963</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -5748,626 +5745,701 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Capital expenditure guide, 2026</t>
-        </is>
-      </c>
-      <c r="B40" s="25" t="n">
-        <v>300</v>
+          <t>Days payable</t>
+        </is>
+      </c>
+      <c r="B40" s="29" t="n">
+        <v>92.49608922133605</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>USD million</t>
+          <t>days</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Maintenance capital expenditure, steady state</t>
+          <t>Capital expenditure guide, 2026</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>USD million a year</t>
+          <t>USD million</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Property, plant and equipment, opening</t>
+          <t>Maintenance capital expenditure, steady state</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
-        <v>6082.232</v>
+        <v>320</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>USD million at 31 December 2025</t>
+          <t>USD million a year</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Depreciation rate on the property balance</t>
-        </is>
-      </c>
-      <c r="B43" s="26" t="n">
-        <v>0.06576533088510929</v>
+          <t>Property, plant and equipment, opening</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="n">
+        <v>6082.232</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>the H1-2026 charge annualised, over the opening property balance</t>
+          <t>USD million at 31 December 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Equity attributable to owners, 30 June 2026</t>
+        </is>
+      </c>
+      <c r="B44" s="25" t="n">
+        <v>3725.997</v>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>USD million — the book-value lens reads this, on the SAME date as the bridge</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>TERMINAL BLOCK AND THE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Return on equity, FY2023</t>
+        </is>
+      </c>
+      <c r="B45" s="28" t="n">
+        <v>0.2186715799422921</v>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>profit attributable to owners over opening equity, from the audited statements</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Terminal growth rate</t>
-        </is>
-      </c>
-      <c r="B46" s="26" t="n">
-        <v>0.02</v>
+          <t>Return on equity, FY2024</t>
+        </is>
+      </c>
+      <c r="B46" s="28" t="n">
+        <v>0.2745570756528634</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>long-run dollar inflation; owned capacity is fixed</t>
+          <t>profit attributable to owners over opening equity, from the audited statements</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Terminal return on capital</t>
+          <t>Return on equity, FY2025</t>
         </is>
       </c>
       <c r="B47" s="28" t="n">
-        <v>0.12</v>
+        <v>0.2663775878303191</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>sets the reinvestment the terminal block must fund</t>
+          <t>profit attributable to owners over opening equity, from the audited statements</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Net debt</t>
-        </is>
-      </c>
-      <c r="B48" s="25" t="n">
-        <v>3275</v>
+          <t>Depreciation rate on the property balance</t>
+        </is>
+      </c>
+      <c r="B48" s="26" t="n">
+        <v>0.06576533088510929</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>USD million at 30 June 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Lease liabilities</t>
-        </is>
-      </c>
-      <c r="B49" s="29" t="n">
-        <v>222.68</v>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>USD million</t>
+          <t>the H1-2026 charge annualised, over the opening property balance</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Non-controlling interests</t>
-        </is>
-      </c>
-      <c r="B50" s="29" t="n">
-        <v>26.832</v>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>USD million at book</t>
-        </is>
-      </c>
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>TERMINAL BLOCK AND THE BRIDGE</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n"/>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Borouge 4 earnings accretion after ramp-up</t>
-        </is>
-      </c>
-      <c r="B51" s="28" t="n">
-        <v>0.1</v>
+          <t>Terminal growth rate</t>
+        </is>
+      </c>
+      <c r="B51" s="26" t="n">
+        <v>0.02</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>the sponsors' own figure</t>
+          <t>long-run dollar inflation; owned capacity is fixed</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Borouge 4 cumulative net profit, first three years</t>
-        </is>
-      </c>
-      <c r="B52" s="25" t="n">
-        <v>400</v>
+          <t>Terminal return on capital</t>
+        </is>
+      </c>
+      <c r="B52" s="28" t="n">
+        <v>0.12</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>USD million; the second quantification</t>
+          <t>sets the reinvestment the terminal block must fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B53" s="25" t="n">
+        <v>3275</v>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>USD million at 30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>FORECAST DRIVERS — NORMALISATION CONSTRUCTION</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="n"/>
-      <c r="C54" s="5" t="n"/>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="n"/>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="5" t="n"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Lease liabilities</t>
+        </is>
+      </c>
+      <c r="B54" s="29" t="n">
+        <v>222.68</v>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>USD million</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr"/>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>2030</t>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Non-controlling interests</t>
+        </is>
+      </c>
+      <c r="B55" s="29" t="n">
+        <v>26.832</v>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>USD million at book</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Polyethylene utilisation</t>
+          <t>Borouge 4 earnings accretion after ramp-up</t>
         </is>
       </c>
       <c r="B56" s="28" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C56" s="28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="D56" s="28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E56" s="28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="F56" s="28" t="n">
-        <v>1.03</v>
+        <v>0.1</v>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>the sponsors' own figure</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Polypropylene utilisation</t>
-        </is>
-      </c>
-      <c r="B57" s="28" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C57" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" s="28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E57" s="28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="F57" s="28" t="n">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Polyethylene benchmark (USD/t)</t>
-        </is>
-      </c>
-      <c r="B58" s="25" t="n">
-        <v>1010</v>
-      </c>
-      <c r="C58" s="25" t="n">
-        <v>900</v>
-      </c>
-      <c r="D58" s="25" t="n">
-        <v>860</v>
-      </c>
-      <c r="E58" s="25" t="n">
-        <v>870</v>
-      </c>
-      <c r="F58" s="25" t="n">
-        <v>885</v>
+          <t>Borouge 4 cumulative net profit, first three years</t>
+        </is>
+      </c>
+      <c r="B57" s="25" t="n">
+        <v>400</v>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>USD million; the second quantification</t>
+        </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Polypropylene benchmark (USD/t)</t>
-        </is>
-      </c>
-      <c r="B59" s="25" t="n">
-        <v>1050</v>
-      </c>
-      <c r="C59" s="25" t="n">
-        <v>930</v>
-      </c>
-      <c r="D59" s="25" t="n">
-        <v>890</v>
-      </c>
-      <c r="E59" s="25" t="n">
-        <v>900</v>
-      </c>
-      <c r="F59" s="25" t="n">
-        <v>915</v>
-      </c>
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>FORECAST DRIVERS — NORMALISATION CONSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n"/>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="5" t="n"/>
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Polyethylene premium (USD/t)</t>
-        </is>
-      </c>
-      <c r="B60" s="25" t="n">
-        <v>260</v>
-      </c>
-      <c r="C60" s="25" t="n">
-        <v>210</v>
-      </c>
-      <c r="D60" s="25" t="n">
-        <v>200</v>
-      </c>
-      <c r="E60" s="25" t="n">
-        <v>200</v>
-      </c>
-      <c r="F60" s="25" t="n">
-        <v>200</v>
+      <c r="A60" s="7" t="inlineStr"/>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Polypropylene premium (USD/t)</t>
-        </is>
-      </c>
-      <c r="B61" s="25" t="n">
-        <v>165</v>
-      </c>
-      <c r="C61" s="25" t="n">
-        <v>145</v>
-      </c>
-      <c r="D61" s="25" t="n">
-        <v>140</v>
-      </c>
-      <c r="E61" s="25" t="n">
-        <v>140</v>
-      </c>
-      <c r="F61" s="25" t="n">
-        <v>140</v>
+          <t>Polyethylene utilisation</t>
+        </is>
+      </c>
+      <c r="B61" s="28" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C61" s="28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="D61" s="28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E61" s="28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F61" s="28" t="n">
+        <v>1.03</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Selling and distribution (USD/t sold)</t>
-        </is>
-      </c>
-      <c r="B62" s="25" t="n">
-        <v>150</v>
-      </c>
-      <c r="C62" s="25" t="n">
-        <v>100</v>
-      </c>
-      <c r="D62" s="25" t="n">
-        <v>82</v>
-      </c>
-      <c r="E62" s="25" t="n">
-        <v>83</v>
-      </c>
-      <c r="F62" s="25" t="n">
-        <v>85</v>
+          <t>Polypropylene utilisation</t>
+        </is>
+      </c>
+      <c r="B62" s="28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C62" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E62" s="28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F62" s="28" t="n">
+        <v>1.01</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Share of feedstock bought at market price</t>
-        </is>
-      </c>
-      <c r="B63" s="28" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="C63" s="28" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D63" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E63" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F63" s="28" t="n">
-        <v>0.3</v>
+          <t>Polyethylene benchmark (USD/t)</t>
+        </is>
+      </c>
+      <c r="B63" s="25" t="n">
+        <v>1010</v>
+      </c>
+      <c r="C63" s="25" t="n">
+        <v>900</v>
+      </c>
+      <c r="D63" s="25" t="n">
+        <v>860</v>
+      </c>
+      <c r="E63" s="25" t="n">
+        <v>870</v>
+      </c>
+      <c r="F63" s="25" t="n">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Polypropylene benchmark (USD/t)</t>
+        </is>
+      </c>
+      <c r="B64" s="25" t="n">
+        <v>1050</v>
+      </c>
+      <c r="C64" s="25" t="n">
+        <v>930</v>
+      </c>
+      <c r="D64" s="25" t="n">
+        <v>890</v>
+      </c>
+      <c r="E64" s="25" t="n">
+        <v>900</v>
+      </c>
+      <c r="F64" s="25" t="n">
+        <v>915</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>FORECAST DRIVERS — PROLONGED-DISRUPTION CONSTRUCTION</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="n"/>
-      <c r="C65" s="5" t="n"/>
-      <c r="D65" s="5" t="n"/>
-      <c r="E65" s="5" t="n"/>
-      <c r="F65" s="5" t="n"/>
-      <c r="G65" s="5" t="n"/>
-      <c r="H65" s="5" t="n"/>
-      <c r="I65" s="5" t="n"/>
-      <c r="J65" s="5" t="n"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Polyethylene premium (USD/t)</t>
+        </is>
+      </c>
+      <c r="B65" s="25" t="n">
+        <v>260</v>
+      </c>
+      <c r="C65" s="25" t="n">
+        <v>210</v>
+      </c>
+      <c r="D65" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="E65" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="F65" s="25" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="inlineStr"/>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Polypropylene premium (USD/t)</t>
+        </is>
+      </c>
+      <c r="B66" s="25" t="n">
+        <v>165</v>
+      </c>
+      <c r="C66" s="25" t="n">
+        <v>145</v>
+      </c>
+      <c r="D66" s="25" t="n">
+        <v>140</v>
+      </c>
+      <c r="E66" s="25" t="n">
+        <v>140</v>
+      </c>
+      <c r="F66" s="25" t="n">
+        <v>140</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Polyethylene utilisation</t>
-        </is>
-      </c>
-      <c r="B67" s="28" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C67" s="28" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="D67" s="28" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E67" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="28" t="n">
-        <v>1.02</v>
+          <t>Selling and distribution (USD/t sold)</t>
+        </is>
+      </c>
+      <c r="B67" s="25" t="n">
+        <v>150</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>100</v>
+      </c>
+      <c r="D67" s="25" t="n">
+        <v>82</v>
+      </c>
+      <c r="E67" s="25" t="n">
+        <v>83</v>
+      </c>
+      <c r="F67" s="25" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Polypropylene utilisation</t>
+          <t>Share of feedstock bought at market price</t>
         </is>
       </c>
       <c r="B68" s="28" t="n">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="C68" s="28" t="n">
-        <v>0.9</v>
+        <v>0.35</v>
       </c>
       <c r="D68" s="28" t="n">
-        <v>0.96</v>
+        <v>0.3</v>
       </c>
       <c r="E68" s="28" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="F68" s="28" t="n">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Polyethylene benchmark (USD/t)</t>
-        </is>
-      </c>
-      <c r="B69" s="25" t="n">
-        <v>1060</v>
-      </c>
-      <c r="C69" s="25" t="n">
-        <v>1030</v>
-      </c>
-      <c r="D69" s="25" t="n">
-        <v>960</v>
-      </c>
-      <c r="E69" s="25" t="n">
-        <v>910</v>
-      </c>
-      <c r="F69" s="25" t="n">
-        <v>890</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Polypropylene benchmark (USD/t)</t>
-        </is>
-      </c>
-      <c r="B70" s="25" t="n">
-        <v>1105</v>
-      </c>
-      <c r="C70" s="25" t="n">
-        <v>1070</v>
-      </c>
-      <c r="D70" s="25" t="n">
-        <v>995</v>
-      </c>
-      <c r="E70" s="25" t="n">
-        <v>940</v>
-      </c>
-      <c r="F70" s="25" t="n">
-        <v>920</v>
-      </c>
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>FORECAST DRIVERS — PROLONGED-DISRUPTION CONSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n"/>
+      <c r="C70" s="5" t="n"/>
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="n"/>
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="5" t="n"/>
+      <c r="I70" s="5" t="n"/>
+      <c r="J70" s="5" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Polyethylene premium (USD/t)</t>
-        </is>
-      </c>
-      <c r="B71" s="25" t="n">
-        <v>300</v>
-      </c>
-      <c r="C71" s="25" t="n">
-        <v>275</v>
-      </c>
-      <c r="D71" s="25" t="n">
-        <v>240</v>
-      </c>
-      <c r="E71" s="25" t="n">
-        <v>215</v>
-      </c>
-      <c r="F71" s="25" t="n">
-        <v>200</v>
+      <c r="A71" s="7" t="inlineStr"/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Polypropylene premium (USD/t)</t>
-        </is>
-      </c>
-      <c r="B72" s="25" t="n">
-        <v>195</v>
-      </c>
-      <c r="C72" s="25" t="n">
-        <v>180</v>
-      </c>
-      <c r="D72" s="25" t="n">
-        <v>160</v>
-      </c>
-      <c r="E72" s="25" t="n">
-        <v>148</v>
-      </c>
-      <c r="F72" s="25" t="n">
-        <v>140</v>
+          <t>Polyethylene utilisation</t>
+        </is>
+      </c>
+      <c r="B72" s="28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C72" s="28" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D72" s="28" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E72" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="28" t="n">
+        <v>1.02</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Selling and distribution (USD/t sold)</t>
-        </is>
-      </c>
-      <c r="B73" s="25" t="n">
-        <v>172</v>
-      </c>
-      <c r="C73" s="25" t="n">
-        <v>165</v>
-      </c>
-      <c r="D73" s="25" t="n">
-        <v>140</v>
-      </c>
-      <c r="E73" s="25" t="n">
-        <v>110</v>
-      </c>
-      <c r="F73" s="25" t="n">
-        <v>90</v>
+          <t>Polypropylene utilisation</t>
+        </is>
+      </c>
+      <c r="B73" s="28" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C73" s="28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D73" s="28" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E73" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="28" t="n">
+        <v>1.01</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>Polyethylene benchmark (USD/t)</t>
+        </is>
+      </c>
+      <c r="B74" s="25" t="n">
+        <v>1010</v>
+      </c>
+      <c r="C74" s="25" t="n">
+        <v>900</v>
+      </c>
+      <c r="D74" s="25" t="n">
+        <v>860</v>
+      </c>
+      <c r="E74" s="25" t="n">
+        <v>870</v>
+      </c>
+      <c r="F74" s="25" t="n">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Polypropylene benchmark (USD/t)</t>
+        </is>
+      </c>
+      <c r="B75" s="25" t="n">
+        <v>1050</v>
+      </c>
+      <c r="C75" s="25" t="n">
+        <v>930</v>
+      </c>
+      <c r="D75" s="25" t="n">
+        <v>890</v>
+      </c>
+      <c r="E75" s="25" t="n">
+        <v>900</v>
+      </c>
+      <c r="F75" s="25" t="n">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Polyethylene premium (USD/t)</t>
+        </is>
+      </c>
+      <c r="B76" s="25" t="n">
+        <v>260</v>
+      </c>
+      <c r="C76" s="25" t="n">
+        <v>210</v>
+      </c>
+      <c r="D76" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="E76" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="F76" s="25" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Polypropylene premium (USD/t)</t>
+        </is>
+      </c>
+      <c r="B77" s="25" t="n">
+        <v>165</v>
+      </c>
+      <c r="C77" s="25" t="n">
+        <v>145</v>
+      </c>
+      <c r="D77" s="25" t="n">
+        <v>140</v>
+      </c>
+      <c r="E77" s="25" t="n">
+        <v>140</v>
+      </c>
+      <c r="F77" s="25" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Selling and distribution (USD/t sold)</t>
+        </is>
+      </c>
+      <c r="B78" s="25" t="n">
+        <v>172</v>
+      </c>
+      <c r="C78" s="25" t="n">
+        <v>165</v>
+      </c>
+      <c r="D78" s="25" t="n">
+        <v>140</v>
+      </c>
+      <c r="E78" s="25" t="n">
+        <v>110</v>
+      </c>
+      <c r="F78" s="25" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>Share of feedstock bought at market price</t>
         </is>
       </c>
-      <c r="B74" s="28" t="n">
+      <c r="B79" s="28" t="n">
         <v>0.62</v>
       </c>
-      <c r="C74" s="28" t="n">
+      <c r="C79" s="28" t="n">
         <v>0.58</v>
       </c>
-      <c r="D74" s="28" t="n">
+      <c r="D79" s="28" t="n">
         <v>0.45</v>
       </c>
-      <c r="E74" s="28" t="n">
+      <c r="E79" s="28" t="n">
         <v>0.35</v>
       </c>
-      <c r="F74" s="28" t="n">
+      <c r="F79" s="28" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>Every other number in this workbook is computed from the cells above, from the audited history on the statement sheets, or is one of the three pasted classes named on READ FIRST.</t>
         </is>
@@ -6375,7 +6447,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="A81:I81"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6446,7 +6518,7 @@
         </is>
       </c>
       <c r="B5" s="30">
-        <f>Assumptions!$B$52/1.0</f>
+        <f>Assumptions!$B$57/1.0</f>
         <v/>
       </c>
     </row>
@@ -6457,7 +6529,7 @@
         </is>
       </c>
       <c r="B6" s="30">
-        <f>Assumptions!$B$51*AVERAGE('DCF'!B16:F16)</f>
+        <f>Assumptions!$B$56*AVERAGE('DCF'!B16:F16)</f>
         <v/>
       </c>
     </row>
@@ -6599,8 +6671,13 @@
         </is>
       </c>
       <c r="B15" s="30">
-        <f>$B7*(1+Assumptions!$B$46)/('DCF'!F$21-Assumptions!$B$46)*'DCF'!F$22</f>
-        <v/>
+        <f>$B7*0</f>
+        <v/>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>NIL by construction: the Asset Usage Agreement runs only until the assets are acquired by the parent group, which the company says is not anticipated before 2029. A stream that ends cannot carry a perpetuity</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -6683,19 +6760,19 @@
         </is>
       </c>
       <c r="B21" s="17">
-        <f>-Assumptions!$B$48</f>
+        <f>-Assumptions!$B$53</f>
         <v/>
       </c>
       <c r="C21" s="17">
-        <f>-Assumptions!$B$48</f>
+        <f>-Assumptions!$B$53</f>
         <v/>
       </c>
       <c r="D21" s="17">
-        <f>-Assumptions!$B$48</f>
+        <f>-Assumptions!$B$53</f>
         <v/>
       </c>
       <c r="E21" s="17">
-        <f>-Assumptions!$B$48</f>
+        <f>-Assumptions!$B$53</f>
         <v/>
       </c>
     </row>
@@ -6706,19 +6783,19 @@
         </is>
       </c>
       <c r="B22" s="30">
-        <f>-Assumptions!$B$49</f>
+        <f>-Assumptions!$B$54</f>
         <v/>
       </c>
       <c r="C22" s="30">
-        <f>-Assumptions!$B$49</f>
+        <f>-Assumptions!$B$54</f>
         <v/>
       </c>
       <c r="D22" s="30">
-        <f>-Assumptions!$B$49</f>
+        <f>-Assumptions!$B$54</f>
         <v/>
       </c>
       <c r="E22" s="30">
-        <f>-Assumptions!$B$49</f>
+        <f>-Assumptions!$B$54</f>
         <v/>
       </c>
     </row>
@@ -6729,19 +6806,19 @@
         </is>
       </c>
       <c r="B23" s="30">
-        <f>-Assumptions!$B$50</f>
+        <f>-Assumptions!$B$55</f>
         <v/>
       </c>
       <c r="C23" s="30">
-        <f>-Assumptions!$B$50</f>
+        <f>-Assumptions!$B$55</f>
         <v/>
       </c>
       <c r="D23" s="30">
-        <f>-Assumptions!$B$50</f>
+        <f>-Assumptions!$B$55</f>
         <v/>
       </c>
       <c r="E23" s="30">
-        <f>-Assumptions!$B$50</f>
+        <f>-Assumptions!$B$55</f>
         <v/>
       </c>
     </row>
@@ -7270,23 +7347,23 @@
         </is>
       </c>
       <c r="B26" s="17">
-        <f>Assumptions!$B$22*Assumptions!B$56</f>
+        <f>Assumptions!$B$22*Assumptions!B$61</f>
         <v/>
       </c>
       <c r="C26" s="17">
-        <f>Assumptions!$B$22*Assumptions!C$56</f>
+        <f>Assumptions!$B$22*Assumptions!C$61</f>
         <v/>
       </c>
       <c r="D26" s="17">
-        <f>Assumptions!$B$22*Assumptions!D$56</f>
+        <f>Assumptions!$B$22*Assumptions!D$61</f>
         <v/>
       </c>
       <c r="E26" s="17">
-        <f>Assumptions!$B$22*Assumptions!E$56</f>
+        <f>Assumptions!$B$22*Assumptions!E$61</f>
         <v/>
       </c>
       <c r="F26" s="17">
-        <f>Assumptions!$B$22*Assumptions!F$56</f>
+        <f>Assumptions!$B$22*Assumptions!F$61</f>
         <v/>
       </c>
     </row>
@@ -7297,23 +7374,23 @@
         </is>
       </c>
       <c r="B27" s="17">
-        <f>Assumptions!$B$23*Assumptions!B$57</f>
+        <f>Assumptions!$B$23*Assumptions!B$62</f>
         <v/>
       </c>
       <c r="C27" s="17">
-        <f>Assumptions!$B$23*Assumptions!C$57</f>
+        <f>Assumptions!$B$23*Assumptions!C$62</f>
         <v/>
       </c>
       <c r="D27" s="17">
-        <f>Assumptions!$B$23*Assumptions!D$57</f>
+        <f>Assumptions!$B$23*Assumptions!D$62</f>
         <v/>
       </c>
       <c r="E27" s="17">
-        <f>Assumptions!$B$23*Assumptions!E$57</f>
+        <f>Assumptions!$B$23*Assumptions!E$62</f>
         <v/>
       </c>
       <c r="F27" s="17">
-        <f>Assumptions!$B$23*Assumptions!F$57</f>
+        <f>Assumptions!$B$23*Assumptions!F$62</f>
         <v/>
       </c>
     </row>
@@ -7351,23 +7428,23 @@
         </is>
       </c>
       <c r="B29" s="30">
-        <f>(Assumptions!B$58+Assumptions!B$60)*Assumptions!$B$24</f>
+        <f>(Assumptions!B$63+Assumptions!B$65)*Assumptions!$B$25</f>
         <v/>
       </c>
       <c r="C29" s="30">
-        <f>(Assumptions!C$58+Assumptions!C$60)*Assumptions!$B$24</f>
+        <f>(Assumptions!C$63+Assumptions!C$65)*Assumptions!$B$25</f>
         <v/>
       </c>
       <c r="D29" s="30">
-        <f>(Assumptions!D$58+Assumptions!D$60)*Assumptions!$B$24</f>
+        <f>(Assumptions!D$63+Assumptions!D$65)*Assumptions!$B$25</f>
         <v/>
       </c>
       <c r="E29" s="30">
-        <f>(Assumptions!E$58+Assumptions!E$60)*Assumptions!$B$24</f>
+        <f>(Assumptions!E$63+Assumptions!E$65)*Assumptions!$B$25</f>
         <v/>
       </c>
       <c r="F29" s="30">
-        <f>(Assumptions!F$58+Assumptions!F$60)*Assumptions!$B$24</f>
+        <f>(Assumptions!F$63+Assumptions!F$65)*Assumptions!$B$25</f>
         <v/>
       </c>
     </row>
@@ -7378,23 +7455,23 @@
         </is>
       </c>
       <c r="B30" s="30">
-        <f>(Assumptions!B$59+Assumptions!B$61)*Assumptions!$B$25</f>
+        <f>(Assumptions!B$64+Assumptions!B$66)*Assumptions!$B$26</f>
         <v/>
       </c>
       <c r="C30" s="30">
-        <f>(Assumptions!C$59+Assumptions!C$61)*Assumptions!$B$25</f>
+        <f>(Assumptions!C$64+Assumptions!C$66)*Assumptions!$B$26</f>
         <v/>
       </c>
       <c r="D30" s="30">
-        <f>(Assumptions!D$59+Assumptions!D$61)*Assumptions!$B$25</f>
+        <f>(Assumptions!D$64+Assumptions!D$66)*Assumptions!$B$26</f>
         <v/>
       </c>
       <c r="E30" s="30">
-        <f>(Assumptions!E$59+Assumptions!E$61)*Assumptions!$B$25</f>
+        <f>(Assumptions!E$64+Assumptions!E$66)*Assumptions!$B$26</f>
         <v/>
       </c>
       <c r="F30" s="30">
-        <f>(Assumptions!F$59+Assumptions!F$61)*Assumptions!$B$25</f>
+        <f>(Assumptions!F$64+Assumptions!F$66)*Assumptions!$B$26</f>
         <v/>
       </c>
     </row>
@@ -7405,23 +7482,23 @@
         </is>
       </c>
       <c r="B31" s="30">
-        <f>(1-Assumptions!B$63)*(Assumptions!$B$28*(1+Assumptions!$B$30)^1)+Assumptions!B$63*(Assumptions!$B$28*Assumptions!B$59/Assumptions!$B$29)</f>
+        <f>(1-Assumptions!B$68)*(Assumptions!$B$29*(1+Assumptions!$B$31)^1)+Assumptions!B$68*(Assumptions!$B$29*Assumptions!B$64/Assumptions!$B$30)</f>
         <v/>
       </c>
       <c r="C31" s="30">
-        <f>(1-Assumptions!C$63)*(Assumptions!$B$28*(1+Assumptions!$B$30)^2)+Assumptions!C$63*(Assumptions!$B$28*Assumptions!C$59/Assumptions!$B$29)</f>
+        <f>(1-Assumptions!C$68)*(Assumptions!$B$29*(1+Assumptions!$B$31)^2)+Assumptions!C$68*(Assumptions!$B$29*Assumptions!C$64/Assumptions!$B$30)</f>
         <v/>
       </c>
       <c r="D31" s="30">
-        <f>(1-Assumptions!D$63)*(Assumptions!$B$28*(1+Assumptions!$B$30)^3)+Assumptions!D$63*(Assumptions!$B$28*Assumptions!D$59/Assumptions!$B$29)</f>
+        <f>(1-Assumptions!D$68)*(Assumptions!$B$29*(1+Assumptions!$B$31)^3)+Assumptions!D$68*(Assumptions!$B$29*Assumptions!D$64/Assumptions!$B$30)</f>
         <v/>
       </c>
       <c r="E31" s="30">
-        <f>(1-Assumptions!E$63)*(Assumptions!$B$28*(1+Assumptions!$B$30)^4)+Assumptions!E$63*(Assumptions!$B$28*Assumptions!E$59/Assumptions!$B$29)</f>
+        <f>(1-Assumptions!E$68)*(Assumptions!$B$29*(1+Assumptions!$B$31)^4)+Assumptions!E$68*(Assumptions!$B$29*Assumptions!E$64/Assumptions!$B$30)</f>
         <v/>
       </c>
       <c r="F31" s="30">
-        <f>(1-Assumptions!F$63)*(Assumptions!$B$28*(1+Assumptions!$B$30)^5)+Assumptions!F$63*(Assumptions!$B$28*Assumptions!F$59/Assumptions!$B$29)</f>
+        <f>(1-Assumptions!F$68)*(Assumptions!$B$29*(1+Assumptions!$B$31)^5)+Assumptions!F$68*(Assumptions!$B$29*Assumptions!F$64/Assumptions!$B$30)</f>
         <v/>
       </c>
     </row>
@@ -7476,23 +7553,23 @@
         </is>
       </c>
       <c r="B35" s="17">
-        <f>Assumptions!$B$22*Assumptions!B$67</f>
+        <f>Assumptions!$B$22*Assumptions!B$72</f>
         <v/>
       </c>
       <c r="C35" s="17">
-        <f>Assumptions!$B$22*Assumptions!C$67</f>
+        <f>Assumptions!$B$22*Assumptions!C$72</f>
         <v/>
       </c>
       <c r="D35" s="17">
-        <f>Assumptions!$B$22*Assumptions!D$67</f>
+        <f>Assumptions!$B$22*Assumptions!D$72</f>
         <v/>
       </c>
       <c r="E35" s="17">
-        <f>Assumptions!$B$22*Assumptions!E$67</f>
+        <f>Assumptions!$B$22*Assumptions!E$72</f>
         <v/>
       </c>
       <c r="F35" s="17">
-        <f>Assumptions!$B$22*Assumptions!F$67</f>
+        <f>Assumptions!$B$22*Assumptions!F$72</f>
         <v/>
       </c>
     </row>
@@ -7503,23 +7580,23 @@
         </is>
       </c>
       <c r="B36" s="17">
-        <f>Assumptions!$B$23*Assumptions!B$68</f>
+        <f>Assumptions!$B$23*Assumptions!B$73</f>
         <v/>
       </c>
       <c r="C36" s="17">
-        <f>Assumptions!$B$23*Assumptions!C$68</f>
+        <f>Assumptions!$B$23*Assumptions!C$73</f>
         <v/>
       </c>
       <c r="D36" s="17">
-        <f>Assumptions!$B$23*Assumptions!D$68</f>
+        <f>Assumptions!$B$23*Assumptions!D$73</f>
         <v/>
       </c>
       <c r="E36" s="17">
-        <f>Assumptions!$B$23*Assumptions!E$68</f>
+        <f>Assumptions!$B$23*Assumptions!E$73</f>
         <v/>
       </c>
       <c r="F36" s="17">
-        <f>Assumptions!$B$23*Assumptions!F$68</f>
+        <f>Assumptions!$B$23*Assumptions!F$73</f>
         <v/>
       </c>
     </row>
@@ -7557,23 +7634,23 @@
         </is>
       </c>
       <c r="B38" s="30">
-        <f>(Assumptions!B$69+Assumptions!B$71)*Assumptions!$B$24</f>
+        <f>(Assumptions!B$74+Assumptions!B$76)*Assumptions!$B$25</f>
         <v/>
       </c>
       <c r="C38" s="30">
-        <f>(Assumptions!C$69+Assumptions!C$71)*Assumptions!$B$24</f>
+        <f>(Assumptions!C$74+Assumptions!C$76)*Assumptions!$B$25</f>
         <v/>
       </c>
       <c r="D38" s="30">
-        <f>(Assumptions!D$69+Assumptions!D$71)*Assumptions!$B$24</f>
+        <f>(Assumptions!D$74+Assumptions!D$76)*Assumptions!$B$25</f>
         <v/>
       </c>
       <c r="E38" s="30">
-        <f>(Assumptions!E$69+Assumptions!E$71)*Assumptions!$B$24</f>
+        <f>(Assumptions!E$74+Assumptions!E$76)*Assumptions!$B$25</f>
         <v/>
       </c>
       <c r="F38" s="30">
-        <f>(Assumptions!F$69+Assumptions!F$71)*Assumptions!$B$24</f>
+        <f>(Assumptions!F$74+Assumptions!F$76)*Assumptions!$B$25</f>
         <v/>
       </c>
     </row>
@@ -7584,23 +7661,23 @@
         </is>
       </c>
       <c r="B39" s="30">
-        <f>(Assumptions!B$70+Assumptions!B$72)*Assumptions!$B$25</f>
+        <f>(Assumptions!B$75+Assumptions!B$77)*Assumptions!$B$26</f>
         <v/>
       </c>
       <c r="C39" s="30">
-        <f>(Assumptions!C$70+Assumptions!C$72)*Assumptions!$B$25</f>
+        <f>(Assumptions!C$75+Assumptions!C$77)*Assumptions!$B$26</f>
         <v/>
       </c>
       <c r="D39" s="30">
-        <f>(Assumptions!D$70+Assumptions!D$72)*Assumptions!$B$25</f>
+        <f>(Assumptions!D$75+Assumptions!D$77)*Assumptions!$B$26</f>
         <v/>
       </c>
       <c r="E39" s="30">
-        <f>(Assumptions!E$70+Assumptions!E$72)*Assumptions!$B$25</f>
+        <f>(Assumptions!E$75+Assumptions!E$77)*Assumptions!$B$26</f>
         <v/>
       </c>
       <c r="F39" s="30">
-        <f>(Assumptions!F$70+Assumptions!F$72)*Assumptions!$B$25</f>
+        <f>(Assumptions!F$75+Assumptions!F$77)*Assumptions!$B$26</f>
         <v/>
       </c>
     </row>
@@ -7611,23 +7688,23 @@
         </is>
       </c>
       <c r="B40" s="30">
-        <f>(1-Assumptions!B$74)*(Assumptions!$B$28*(1+Assumptions!$B$30)^1)+Assumptions!B$74*(Assumptions!$B$28*Assumptions!B$70/Assumptions!$B$29)</f>
+        <f>(1-Assumptions!B$79)*(Assumptions!$B$29*(1+Assumptions!$B$31)^1)+Assumptions!B$79*(Assumptions!$B$29*Assumptions!B$75/Assumptions!$B$30)</f>
         <v/>
       </c>
       <c r="C40" s="30">
-        <f>(1-Assumptions!C$74)*(Assumptions!$B$28*(1+Assumptions!$B$30)^2)+Assumptions!C$74*(Assumptions!$B$28*Assumptions!C$70/Assumptions!$B$29)</f>
+        <f>(1-Assumptions!C$79)*(Assumptions!$B$29*(1+Assumptions!$B$31)^2)+Assumptions!C$79*(Assumptions!$B$29*Assumptions!C$75/Assumptions!$B$30)</f>
         <v/>
       </c>
       <c r="D40" s="30">
-        <f>(1-Assumptions!D$74)*(Assumptions!$B$28*(1+Assumptions!$B$30)^3)+Assumptions!D$74*(Assumptions!$B$28*Assumptions!D$70/Assumptions!$B$29)</f>
+        <f>(1-Assumptions!D$79)*(Assumptions!$B$29*(1+Assumptions!$B$31)^3)+Assumptions!D$79*(Assumptions!$B$29*Assumptions!D$75/Assumptions!$B$30)</f>
         <v/>
       </c>
       <c r="E40" s="30">
-        <f>(1-Assumptions!E$74)*(Assumptions!$B$28*(1+Assumptions!$B$30)^4)+Assumptions!E$74*(Assumptions!$B$28*Assumptions!E$70/Assumptions!$B$29)</f>
+        <f>(1-Assumptions!E$79)*(Assumptions!$B$29*(1+Assumptions!$B$31)^4)+Assumptions!E$79*(Assumptions!$B$29*Assumptions!E$75/Assumptions!$B$30)</f>
         <v/>
       </c>
       <c r="F40" s="30">
-        <f>(1-Assumptions!F$74)*(Assumptions!$B$28*(1+Assumptions!$B$30)^5)+Assumptions!F$74*(Assumptions!$B$28*Assumptions!F$70/Assumptions!$B$29)</f>
+        <f>(1-Assumptions!F$79)*(Assumptions!$B$29*(1+Assumptions!$B$31)^5)+Assumptions!F$79*(Assumptions!$B$29*Assumptions!F$75/Assumptions!$B$30)</f>
         <v/>
       </c>
     </row>
@@ -7653,7 +7730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -7854,18 +7931,23 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Less: net debt, leases and non-controlling interests</t>
-        </is>
-      </c>
-      <c r="B19" s="17">
-        <f>-Assumptions!$B$48-Assumptions!$B$49-Assumptions!$B$50</f>
-        <v/>
+          <t>Add: the Borouge 4 fee stream, on the same basis as the cash-flow lens</t>
+        </is>
+      </c>
+      <c r="B19" s="37">
+        <f>'SOTP Bridge'!$B$16</f>
+        <v/>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>The same separable asset the cash-flow lens carries. Omitting it here valued three different companies under three lenses</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Equity value</t>
+          <t>Enterprise value including the fee stream</t>
         </is>
       </c>
       <c r="B20" s="17">
@@ -7874,275 +7956,297 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Less: net debt, leases and non-controlling interests</t>
+        </is>
+      </c>
+      <c r="B21" s="17">
+        <f>-Assumptions!$B$53-Assumptions!$B$54-Assumptions!$B$55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Equity value</t>
+        </is>
+      </c>
+      <c r="B22" s="17">
+        <f>B20+B21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Relative lens — value per share (AED)</t>
         </is>
       </c>
-      <c r="B21" s="21">
-        <f>B20/Assumptions!$B$7*Assumptions!$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="B23" s="21">
+        <f>B22/Assumptions!$B$7*Assumptions!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>NORMALISED EARNINGS POWER</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Mid-cycle is DERIVED from the audited record, not asserted: utilisation is the mean of the two most recent audited years and the benchmark is the mean of the three audited annual averages. Both therefore contain a turnaround year and a soft-price year, and neither contains the 2026 disruption.</t>
         </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Mid-cycle polyethylene utilisation</t>
-        </is>
-      </c>
-      <c r="B25" s="28" t="n">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Mid-cycle polypropylene utilisation</t>
-        </is>
-      </c>
-      <c r="B26" s="28" t="n">
-        <v>0.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Mid-cycle polyethylene benchmark (USD/t)</t>
-        </is>
-      </c>
-      <c r="B27" s="25" t="n">
-        <v>878</v>
+          <t>Mid-cycle polyethylene utilisation</t>
+        </is>
+      </c>
+      <c r="B27" s="28" t="n">
+        <v>1.06</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Mid-cycle polypropylene benchmark (USD/t)</t>
-        </is>
-      </c>
-      <c r="B28" s="25" t="n">
-        <v>879.6666666666666</v>
+          <t>Mid-cycle polypropylene utilisation</t>
+        </is>
+      </c>
+      <c r="B28" s="28" t="n">
+        <v>0.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Through-the-cycle polyethylene premium (USD/t)</t>
+          <t>Mid-cycle polyethylene benchmark (USD/t)</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
-        <v>200</v>
+        <v>878</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Through-the-cycle polypropylene premium (USD/t)</t>
+          <t>Mid-cycle polypropylene benchmark (USD/t)</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
-        <v>140</v>
+        <v>879.6666666666666</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Mid-cycle selling and distribution (USD/t)</t>
-        </is>
-      </c>
-      <c r="B31" s="29" t="n">
-        <v>81.25553282267887</v>
+          <t>Through-the-cycle polyethylene premium (USD/t)</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Mid-cycle depreciation and amortisation (USD m)</t>
+          <t>Through-the-cycle polypropylene premium (USD/t)</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
-        <v>400</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Mid-cycle polyethylene volume (kt)</t>
-        </is>
-      </c>
-      <c r="B33" s="17">
-        <f>B25*Assumptions!$B$22</f>
-        <v/>
+          <t>Mid-cycle selling and distribution (USD/t)</t>
+        </is>
+      </c>
+      <c r="B33" s="29" t="n">
+        <v>81.25553282267887</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Mid-cycle polypropylene volume (kt)</t>
-        </is>
-      </c>
-      <c r="B34" s="17">
-        <f>B26*Assumptions!$B$23</f>
-        <v/>
+          <t>Mid-cycle depreciation and amortisation (USD m)</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Mid-cycle volume (kt)</t>
-        </is>
-      </c>
-      <c r="B35" s="32">
-        <f>B33+B34</f>
+          <t>Mid-cycle polyethylene volume (kt)</t>
+        </is>
+      </c>
+      <c r="B35" s="17">
+        <f>B27*Assumptions!$B$22</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Mid-cycle revenue (USD million)</t>
+          <t>Mid-cycle polypropylene volume (kt)</t>
         </is>
       </c>
       <c r="B36" s="17">
-        <f>(B33*(B27+B29)*Assumptions!$B$24+B34*(B28+B30)*Assumptions!$B$25)/1000</f>
+        <f>B28*Assumptions!$B$23</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Less: feedstock</t>
-        </is>
-      </c>
-      <c r="B37" s="17">
-        <f>Assumptions!$B$28*B35/1000</f>
+          <t>Mid-cycle volume (kt)</t>
+        </is>
+      </c>
+      <c r="B37" s="32">
+        <f>B35+B36</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Less: other production cost</t>
+          <t>Mid-cycle revenue (USD million)</t>
         </is>
       </c>
       <c r="B38" s="17">
-        <f>Assumptions!$B$26+Assumptions!$B$27*B35</f>
+        <f>(B35*(B29+B31)*Assumptions!$B$25+B36*(B30+B32)*Assumptions!$B$26)/1000</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Less: selling and distribution</t>
+          <t>Less: feedstock</t>
         </is>
       </c>
       <c r="B39" s="17">
-        <f>B31*B35/1000</f>
+        <f>Assumptions!$B$29*B37/1000</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Less: general and administrative</t>
-        </is>
-      </c>
-      <c r="B40" s="37">
-        <f>Assumptions!$B$34</f>
+          <t>Less: other production cost</t>
+        </is>
+      </c>
+      <c r="B40" s="17">
+        <f>Assumptions!$B$27+Assumptions!$B$28*B37</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>Mid-cycle EBITDA</t>
-        </is>
-      </c>
-      <c r="B41" s="32">
-        <f>B36-B37-B38-B39-B40</f>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Less: selling and distribution</t>
+        </is>
+      </c>
+      <c r="B41" s="17">
+        <f>B33*B37/1000</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Mid-cycle EBIT</t>
-        </is>
-      </c>
-      <c r="B42" s="17">
-        <f>B41-B32</f>
+          <t>Less: general and administrative</t>
+        </is>
+      </c>
+      <c r="B42" s="37">
+        <f>Assumptions!$B$35</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Mid-cycle NOPAT</t>
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Mid-cycle EBITDA</t>
         </is>
       </c>
       <c r="B43" s="32">
-        <f>B42*(1-Assumptions!$B$19)</f>
+        <f>B38-B39-B40-B41-B42</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
+          <t>Mid-cycle EBIT</t>
+        </is>
+      </c>
+      <c r="B44" s="17">
+        <f>B43-B34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Mid-cycle NOPAT</t>
+        </is>
+      </c>
+      <c r="B45" s="32">
+        <f>B44*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
           <t>Enterprise value = NOPAT x (1 - reinvestment) / (cost of capital - growth)</t>
         </is>
       </c>
-      <c r="B44" s="17">
-        <f>B43/('Fundamental Valuation'!$B$29-Assumptions!$B$46)*(1-Assumptions!$B$46/Assumptions!$B$47)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="B46" s="17">
+        <f>B45/('Fundamental Valuation'!$B$29-Assumptions!$B$51)*(1-Assumptions!$B$51/Assumptions!$B$52)+'SOTP Bridge'!$B$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Normalised earnings lens — own-stock beta (AED)</t>
         </is>
       </c>
-      <c r="B45" s="21">
-        <f>(B44-Assumptions!$B$48-Assumptions!$B$49-Assumptions!$B$50)/Assumptions!$B$7*Assumptions!$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="B47" s="21">
+        <f>(B46-Assumptions!$B$53-Assumptions!$B$54-Assumptions!$B$55)/Assumptions!$B$7*Assumptions!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Normalised earnings lens — sector bottom-up beta (AED)</t>
         </is>
       </c>
-      <c r="B46" s="21">
-        <f>(B43/('Fundamental Valuation'!$C$29-Assumptions!$B$46)*(1-Assumptions!$B$46/Assumptions!$B$47)-Assumptions!$B$48-Assumptions!$B$49-Assumptions!$B$50)/Assumptions!$B$7*Assumptions!$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="B48" s="21">
+        <f>(B45/('Fundamental Valuation'!$C$29-Assumptions!$B$51)*(1-Assumptions!$B$51/Assumptions!$B$52)+'SOTP Bridge'!$B$16-Assumptions!$B$53-Assumptions!$B$54-Assumptions!$B$55)/Assumptions!$B$7*Assumptions!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>Every line of the normalised block above is a live formula off the same capacity, realisation residual and cost stack the forecast uses. Change a driver on Assumptions and this lens moves with it.</t>
         </is>
@@ -8150,8 +8254,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A47:I47"/>
-    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A49:I49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8250,23 +8354,23 @@
         </is>
       </c>
       <c r="B6" s="17">
-        <f>(Segments!B$26*Segments!B$29+Segments!B$27*Segments!B$30)/1000+Assumptions!$B$36*(1-0.1)^1</f>
+        <f>(Segments!B$26*Segments!B$29+Segments!B$27*Segments!B$30)/1000*Assumptions!$B$24+Assumptions!$B$37*(1-0.1)^1</f>
         <v/>
       </c>
       <c r="C6" s="17">
-        <f>(Segments!C$26*Segments!C$29+Segments!C$27*Segments!C$30)/1000+Assumptions!$B$36*(1-0.1)^2</f>
+        <f>(Segments!C$26*Segments!C$29+Segments!C$27*Segments!C$30)/1000*Assumptions!$B$24+Assumptions!$B$37*(1-0.1)^2</f>
         <v/>
       </c>
       <c r="D6" s="17">
-        <f>(Segments!D$26*Segments!D$29+Segments!D$27*Segments!D$30)/1000+Assumptions!$B$36*(1-0.1)^3</f>
+        <f>(Segments!D$26*Segments!D$29+Segments!D$27*Segments!D$30)/1000*Assumptions!$B$24+Assumptions!$B$37*(1-0.1)^3</f>
         <v/>
       </c>
       <c r="E6" s="17">
-        <f>(Segments!E$26*Segments!E$29+Segments!E$27*Segments!E$30)/1000+Assumptions!$B$36*(1-0.1)^4</f>
+        <f>(Segments!E$26*Segments!E$29+Segments!E$27*Segments!E$30)/1000*Assumptions!$B$24+Assumptions!$B$37*(1-0.1)^4</f>
         <v/>
       </c>
       <c r="F6" s="17">
-        <f>(Segments!F$26*Segments!F$29+Segments!F$27*Segments!F$30)/1000+Assumptions!$B$36*(1-0.1)^5</f>
+        <f>(Segments!F$26*Segments!F$29+Segments!F$27*Segments!F$30)/1000*Assumptions!$B$24+Assumptions!$B$37*(1-0.1)^5</f>
         <v/>
       </c>
     </row>
@@ -8304,23 +8408,23 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>Assumptions!$B$26*(1+Assumptions!$B$31)^1+Assumptions!$B$27*Segments!B$28</f>
+        <f>Assumptions!$B$27*(1+Assumptions!$B$32)^1+Assumptions!$B$28*Segments!B$28</f>
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>Assumptions!$B$26*(1+Assumptions!$B$31)^2+Assumptions!$B$27*Segments!C$28</f>
+        <f>Assumptions!$B$27*(1+Assumptions!$B$32)^2+Assumptions!$B$28*Segments!C$28</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>Assumptions!$B$26*(1+Assumptions!$B$31)^3+Assumptions!$B$27*Segments!D$28</f>
+        <f>Assumptions!$B$27*(1+Assumptions!$B$32)^3+Assumptions!$B$28*Segments!D$28</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>Assumptions!$B$26*(1+Assumptions!$B$31)^4+Assumptions!$B$27*Segments!E$28</f>
+        <f>Assumptions!$B$27*(1+Assumptions!$B$32)^4+Assumptions!$B$28*Segments!E$28</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>Assumptions!$B$26*(1+Assumptions!$B$31)^5+Assumptions!$B$27*Segments!F$28</f>
+        <f>Assumptions!$B$27*(1+Assumptions!$B$32)^5+Assumptions!$B$28*Segments!F$28</f>
         <v/>
       </c>
     </row>
@@ -8331,23 +8435,23 @@
         </is>
       </c>
       <c r="B9" s="17">
-        <f>Assumptions!B$62*Segments!B$28/1000</f>
+        <f>Assumptions!B$67*Segments!B$28*Assumptions!$B$24/1000</f>
         <v/>
       </c>
       <c r="C9" s="17">
-        <f>Assumptions!C$62*Segments!C$28/1000</f>
+        <f>Assumptions!C$67*Segments!C$28*Assumptions!$B$24/1000</f>
         <v/>
       </c>
       <c r="D9" s="17">
-        <f>Assumptions!D$62*Segments!D$28/1000</f>
+        <f>Assumptions!D$67*Segments!D$28*Assumptions!$B$24/1000</f>
         <v/>
       </c>
       <c r="E9" s="17">
-        <f>Assumptions!E$62*Segments!E$28/1000</f>
+        <f>Assumptions!E$67*Segments!E$28*Assumptions!$B$24/1000</f>
         <v/>
       </c>
       <c r="F9" s="17">
-        <f>Assumptions!F$62*Segments!F$28/1000</f>
+        <f>Assumptions!F$67*Segments!F$28*Assumptions!$B$24/1000</f>
         <v/>
       </c>
     </row>
@@ -8358,23 +8462,23 @@
         </is>
       </c>
       <c r="B10" s="30">
-        <f>Assumptions!$B$34*(1+Assumptions!$B$31)^1</f>
+        <f>Assumptions!$B$35*(1+Assumptions!$B$32)^1</f>
         <v/>
       </c>
       <c r="C10" s="30">
-        <f>Assumptions!$B$34*(1+Assumptions!$B$31)^2</f>
+        <f>Assumptions!$B$35*(1+Assumptions!$B$32)^2</f>
         <v/>
       </c>
       <c r="D10" s="30">
-        <f>Assumptions!$B$34*(1+Assumptions!$B$31)^3</f>
+        <f>Assumptions!$B$35*(1+Assumptions!$B$32)^3</f>
         <v/>
       </c>
       <c r="E10" s="30">
-        <f>Assumptions!$B$34*(1+Assumptions!$B$31)^4</f>
+        <f>Assumptions!$B$35*(1+Assumptions!$B$32)^4</f>
         <v/>
       </c>
       <c r="F10" s="30">
-        <f>Assumptions!$B$34*(1+Assumptions!$B$31)^5</f>
+        <f>Assumptions!$B$35*(1+Assumptions!$B$32)^5</f>
         <v/>
       </c>
     </row>
@@ -8385,23 +8489,23 @@
         </is>
       </c>
       <c r="B11" s="30">
-        <f>Assumptions!$B$35*(1+Assumptions!$B$31)^1</f>
+        <f>Assumptions!$B$36*(1+Assumptions!$B$32)^1</f>
         <v/>
       </c>
       <c r="C11" s="30">
-        <f>Assumptions!$B$35*(1+Assumptions!$B$31)^2</f>
+        <f>Assumptions!$B$36*(1+Assumptions!$B$32)^2</f>
         <v/>
       </c>
       <c r="D11" s="30">
-        <f>Assumptions!$B$35*(1+Assumptions!$B$31)^3</f>
+        <f>Assumptions!$B$36*(1+Assumptions!$B$32)^3</f>
         <v/>
       </c>
       <c r="E11" s="30">
-        <f>Assumptions!$B$35*(1+Assumptions!$B$31)^4</f>
+        <f>Assumptions!$B$36*(1+Assumptions!$B$32)^4</f>
         <v/>
       </c>
       <c r="F11" s="30">
-        <f>Assumptions!$B$35*(1+Assumptions!$B$31)^5</f>
+        <f>Assumptions!$B$36*(1+Assumptions!$B$32)^5</f>
         <v/>
       </c>
     </row>
@@ -8466,23 +8570,23 @@
         </is>
       </c>
       <c r="B14" s="17">
-        <f>Assumptions!$B$42*Assumptions!$B$43</f>
+        <f>Assumptions!$B$43*Assumptions!$B$48</f>
         <v/>
       </c>
       <c r="C14" s="17">
-        <f>(Assumptions!$B$42+SUM(B18:B18)-SUM(B14:B14))*Assumptions!$B$43</f>
+        <f>(Assumptions!$B$43+SUM(B18:B18)-SUM(B14:B14))*Assumptions!$B$48</f>
         <v/>
       </c>
       <c r="D14" s="17">
-        <f>(Assumptions!$B$42+SUM(B18:C18)-SUM(B14:C14))*Assumptions!$B$43</f>
+        <f>(Assumptions!$B$43+SUM(B18:C18)-SUM(B14:C14))*Assumptions!$B$48</f>
         <v/>
       </c>
       <c r="E14" s="17">
-        <f>(Assumptions!$B$42+SUM(B18:D18)-SUM(B14:D14))*Assumptions!$B$43</f>
+        <f>(Assumptions!$B$43+SUM(B18:D18)-SUM(B14:D14))*Assumptions!$B$48</f>
         <v/>
       </c>
       <c r="F14" s="17">
-        <f>(Assumptions!$B$42+SUM(B18:E18)-SUM(B14:E14))*Assumptions!$B$43</f>
+        <f>(Assumptions!$B$43+SUM(B18:E18)-SUM(B14:E14))*Assumptions!$B$48</f>
         <v/>
       </c>
     </row>
@@ -8574,23 +8678,23 @@
         </is>
       </c>
       <c r="B18" s="17">
-        <f>Assumptions!$B$40</f>
+        <f>Assumptions!$B$41</f>
         <v/>
       </c>
       <c r="C18" s="17">
-        <f>Assumptions!$B$41</f>
+        <f>Assumptions!$B$42</f>
         <v/>
       </c>
       <c r="D18" s="17">
-        <f>Assumptions!$B$41</f>
+        <f>Assumptions!$B$42</f>
         <v/>
       </c>
       <c r="E18" s="17">
-        <f>Assumptions!$B$41</f>
+        <f>Assumptions!$B$42</f>
         <v/>
       </c>
       <c r="F18" s="17">
-        <f>Assumptions!$B$41</f>
+        <f>Assumptions!$B$42</f>
         <v/>
       </c>
     </row>
@@ -8601,23 +8705,23 @@
         </is>
       </c>
       <c r="B19" s="30">
-        <f>(B6*Assumptions!$B$37/365+(B7+B8)*Assumptions!$B$38/365-(B7+B8)*Assumptions!$B$39/365)-(5847.773*Assumptions!$B$37/365+3099*Assumptions!$B$38/365-3099*Assumptions!$B$39/365)</f>
+        <f>(B6*Assumptions!$B$38/365+(B7+B8)*Assumptions!$B$39/365-(B7+B8)*Assumptions!$B$40/365)-(5847.773*Assumptions!$B$38/365+3099*Assumptions!$B$39/365-3099*Assumptions!$B$40/365)</f>
         <v/>
       </c>
       <c r="C19" s="30">
-        <f>(C6*Assumptions!$B$37/365+(C7+C8)*Assumptions!$B$38/365-(C7+C8)*Assumptions!$B$39/365)-(B6*Assumptions!$B$37/365+(B7+B8)*Assumptions!$B$38/365-(B7+B8)*Assumptions!$B$39/365)</f>
+        <f>(C6*Assumptions!$B$38/365+(C7+C8)*Assumptions!$B$39/365-(C7+C8)*Assumptions!$B$40/365)-(B6*Assumptions!$B$38/365+(B7+B8)*Assumptions!$B$39/365-(B7+B8)*Assumptions!$B$40/365)</f>
         <v/>
       </c>
       <c r="D19" s="30">
-        <f>(D6*Assumptions!$B$37/365+(D7+D8)*Assumptions!$B$38/365-(D7+D8)*Assumptions!$B$39/365)-(C6*Assumptions!$B$37/365+(C7+C8)*Assumptions!$B$38/365-(C7+C8)*Assumptions!$B$39/365)</f>
+        <f>(D6*Assumptions!$B$38/365+(D7+D8)*Assumptions!$B$39/365-(D7+D8)*Assumptions!$B$40/365)-(C6*Assumptions!$B$38/365+(C7+C8)*Assumptions!$B$39/365-(C7+C8)*Assumptions!$B$40/365)</f>
         <v/>
       </c>
       <c r="E19" s="30">
-        <f>(E6*Assumptions!$B$37/365+(E7+E8)*Assumptions!$B$38/365-(E7+E8)*Assumptions!$B$39/365)-(D6*Assumptions!$B$37/365+(D7+D8)*Assumptions!$B$38/365-(D7+D8)*Assumptions!$B$39/365)</f>
+        <f>(E6*Assumptions!$B$38/365+(E7+E8)*Assumptions!$B$39/365-(E7+E8)*Assumptions!$B$40/365)-(D6*Assumptions!$B$38/365+(D7+D8)*Assumptions!$B$39/365-(D7+D8)*Assumptions!$B$40/365)</f>
         <v/>
       </c>
       <c r="F19" s="30">
-        <f>(F6*Assumptions!$B$37/365+(F7+F8)*Assumptions!$B$38/365-(F7+F8)*Assumptions!$B$39/365)-(E6*Assumptions!$B$37/365+(E7+E8)*Assumptions!$B$38/365-(E7+E8)*Assumptions!$B$39/365)</f>
+        <f>(F6*Assumptions!$B$38/365+(F7+F8)*Assumptions!$B$39/365-(F7+F8)*Assumptions!$B$40/365)-(E6*Assumptions!$B$38/365+(E7+E8)*Assumptions!$B$39/365-(E7+E8)*Assumptions!$B$40/365)</f>
         <v/>
       </c>
     </row>
@@ -8763,7 +8867,7 @@
         </is>
       </c>
       <c r="B27" s="17">
-        <f>B26*(1+Assumptions!$B$46)</f>
+        <f>B26*(1+Assumptions!$B$51)</f>
         <v/>
       </c>
     </row>
@@ -8774,7 +8878,7 @@
         </is>
       </c>
       <c r="B28" s="11">
-        <f>Assumptions!$B$46/Assumptions!$B$47</f>
+        <f>Assumptions!$B$51/Assumptions!$B$52</f>
         <v/>
       </c>
     </row>
@@ -8796,7 +8900,7 @@
         </is>
       </c>
       <c r="B30" s="17">
-        <f>B29/(F21-Assumptions!$B$46)</f>
+        <f>B29/(F21-Assumptions!$B$51)</f>
         <v/>
       </c>
     </row>
@@ -8884,23 +8988,23 @@
         </is>
       </c>
       <c r="B37" s="17">
-        <f>(Segments!B$35*Segments!B$38+Segments!B$36*Segments!B$39)/1000+Assumptions!$B$36*(1-0.1)^1</f>
+        <f>(Segments!B$35*Segments!B$38+Segments!B$36*Segments!B$39)/1000*Assumptions!$B$24+Assumptions!$B$37*(1-0.1)^1</f>
         <v/>
       </c>
       <c r="C37" s="17">
-        <f>(Segments!C$35*Segments!C$38+Segments!C$36*Segments!C$39)/1000+Assumptions!$B$36*(1-0.1)^2</f>
+        <f>(Segments!C$35*Segments!C$38+Segments!C$36*Segments!C$39)/1000*Assumptions!$B$24+Assumptions!$B$37*(1-0.1)^2</f>
         <v/>
       </c>
       <c r="D37" s="17">
-        <f>(Segments!D$35*Segments!D$38+Segments!D$36*Segments!D$39)/1000+Assumptions!$B$36*(1-0.1)^3</f>
+        <f>(Segments!D$35*Segments!D$38+Segments!D$36*Segments!D$39)/1000*Assumptions!$B$24+Assumptions!$B$37*(1-0.1)^3</f>
         <v/>
       </c>
       <c r="E37" s="17">
-        <f>(Segments!E$35*Segments!E$38+Segments!E$36*Segments!E$39)/1000+Assumptions!$B$36*(1-0.1)^4</f>
+        <f>(Segments!E$35*Segments!E$38+Segments!E$36*Segments!E$39)/1000*Assumptions!$B$24+Assumptions!$B$37*(1-0.1)^4</f>
         <v/>
       </c>
       <c r="F37" s="17">
-        <f>(Segments!F$35*Segments!F$38+Segments!F$36*Segments!F$39)/1000+Assumptions!$B$36*(1-0.1)^5</f>
+        <f>(Segments!F$35*Segments!F$38+Segments!F$36*Segments!F$39)/1000*Assumptions!$B$24+Assumptions!$B$37*(1-0.1)^5</f>
         <v/>
       </c>
     </row>
@@ -8938,23 +9042,23 @@
         </is>
       </c>
       <c r="B39" s="17">
-        <f>Assumptions!$B$26*(1+Assumptions!$B$31)^1+Assumptions!$B$27*Segments!B$37</f>
+        <f>Assumptions!$B$27*(1+Assumptions!$B$32)^1+Assumptions!$B$28*Segments!B$37</f>
         <v/>
       </c>
       <c r="C39" s="17">
-        <f>Assumptions!$B$26*(1+Assumptions!$B$31)^2+Assumptions!$B$27*Segments!C$37</f>
+        <f>Assumptions!$B$27*(1+Assumptions!$B$32)^2+Assumptions!$B$28*Segments!C$37</f>
         <v/>
       </c>
       <c r="D39" s="17">
-        <f>Assumptions!$B$26*(1+Assumptions!$B$31)^3+Assumptions!$B$27*Segments!D$37</f>
+        <f>Assumptions!$B$27*(1+Assumptions!$B$32)^3+Assumptions!$B$28*Segments!D$37</f>
         <v/>
       </c>
       <c r="E39" s="17">
-        <f>Assumptions!$B$26*(1+Assumptions!$B$31)^4+Assumptions!$B$27*Segments!E$37</f>
+        <f>Assumptions!$B$27*(1+Assumptions!$B$32)^4+Assumptions!$B$28*Segments!E$37</f>
         <v/>
       </c>
       <c r="F39" s="17">
-        <f>Assumptions!$B$26*(1+Assumptions!$B$31)^5+Assumptions!$B$27*Segments!F$37</f>
+        <f>Assumptions!$B$27*(1+Assumptions!$B$32)^5+Assumptions!$B$28*Segments!F$37</f>
         <v/>
       </c>
     </row>
@@ -8965,23 +9069,23 @@
         </is>
       </c>
       <c r="B40" s="17">
-        <f>Assumptions!B$73*Segments!B$37/1000</f>
+        <f>Assumptions!B$78*Segments!B$37*Assumptions!$B$24/1000</f>
         <v/>
       </c>
       <c r="C40" s="17">
-        <f>Assumptions!C$73*Segments!C$37/1000</f>
+        <f>Assumptions!C$78*Segments!C$37*Assumptions!$B$24/1000</f>
         <v/>
       </c>
       <c r="D40" s="17">
-        <f>Assumptions!D$73*Segments!D$37/1000</f>
+        <f>Assumptions!D$78*Segments!D$37*Assumptions!$B$24/1000</f>
         <v/>
       </c>
       <c r="E40" s="17">
-        <f>Assumptions!E$73*Segments!E$37/1000</f>
+        <f>Assumptions!E$78*Segments!E$37*Assumptions!$B$24/1000</f>
         <v/>
       </c>
       <c r="F40" s="17">
-        <f>Assumptions!F$73*Segments!F$37/1000</f>
+        <f>Assumptions!F$78*Segments!F$37*Assumptions!$B$24/1000</f>
         <v/>
       </c>
     </row>
@@ -8992,23 +9096,23 @@
         </is>
       </c>
       <c r="B41" s="30">
-        <f>Assumptions!$B$34*(1+Assumptions!$B$31)^1</f>
+        <f>Assumptions!$B$35*(1+Assumptions!$B$32)^1</f>
         <v/>
       </c>
       <c r="C41" s="30">
-        <f>Assumptions!$B$34*(1+Assumptions!$B$31)^2</f>
+        <f>Assumptions!$B$35*(1+Assumptions!$B$32)^2</f>
         <v/>
       </c>
       <c r="D41" s="30">
-        <f>Assumptions!$B$34*(1+Assumptions!$B$31)^3</f>
+        <f>Assumptions!$B$35*(1+Assumptions!$B$32)^3</f>
         <v/>
       </c>
       <c r="E41" s="30">
-        <f>Assumptions!$B$34*(1+Assumptions!$B$31)^4</f>
+        <f>Assumptions!$B$35*(1+Assumptions!$B$32)^4</f>
         <v/>
       </c>
       <c r="F41" s="30">
-        <f>Assumptions!$B$34*(1+Assumptions!$B$31)^5</f>
+        <f>Assumptions!$B$35*(1+Assumptions!$B$32)^5</f>
         <v/>
       </c>
     </row>
@@ -9019,23 +9123,23 @@
         </is>
       </c>
       <c r="B42" s="30">
-        <f>Assumptions!$B$35*(1+Assumptions!$B$31)^1</f>
+        <f>Assumptions!$B$36*(1+Assumptions!$B$32)^1</f>
         <v/>
       </c>
       <c r="C42" s="30">
-        <f>Assumptions!$B$35*(1+Assumptions!$B$31)^2</f>
+        <f>Assumptions!$B$36*(1+Assumptions!$B$32)^2</f>
         <v/>
       </c>
       <c r="D42" s="30">
-        <f>Assumptions!$B$35*(1+Assumptions!$B$31)^3</f>
+        <f>Assumptions!$B$36*(1+Assumptions!$B$32)^3</f>
         <v/>
       </c>
       <c r="E42" s="30">
-        <f>Assumptions!$B$35*(1+Assumptions!$B$31)^4</f>
+        <f>Assumptions!$B$36*(1+Assumptions!$B$32)^4</f>
         <v/>
       </c>
       <c r="F42" s="30">
-        <f>Assumptions!$B$35*(1+Assumptions!$B$31)^5</f>
+        <f>Assumptions!$B$36*(1+Assumptions!$B$32)^5</f>
         <v/>
       </c>
     </row>
@@ -9100,23 +9204,23 @@
         </is>
       </c>
       <c r="B45" s="17">
-        <f>Assumptions!$B$42*Assumptions!$B$43</f>
+        <f>Assumptions!$B$43*Assumptions!$B$48</f>
         <v/>
       </c>
       <c r="C45" s="17">
-        <f>(Assumptions!$B$42+SUM(B49:B49)-SUM(B45:B45))*Assumptions!$B$43</f>
+        <f>(Assumptions!$B$43+SUM(B49:B49)-SUM(B45:B45))*Assumptions!$B$48</f>
         <v/>
       </c>
       <c r="D45" s="17">
-        <f>(Assumptions!$B$42+SUM(B49:C49)-SUM(B45:C45))*Assumptions!$B$43</f>
+        <f>(Assumptions!$B$43+SUM(B49:C49)-SUM(B45:C45))*Assumptions!$B$48</f>
         <v/>
       </c>
       <c r="E45" s="17">
-        <f>(Assumptions!$B$42+SUM(B49:D49)-SUM(B45:D45))*Assumptions!$B$43</f>
+        <f>(Assumptions!$B$43+SUM(B49:D49)-SUM(B45:D45))*Assumptions!$B$48</f>
         <v/>
       </c>
       <c r="F45" s="17">
-        <f>(Assumptions!$B$42+SUM(B49:E49)-SUM(B45:E45))*Assumptions!$B$43</f>
+        <f>(Assumptions!$B$43+SUM(B49:E49)-SUM(B45:E45))*Assumptions!$B$48</f>
         <v/>
       </c>
     </row>
@@ -9208,23 +9312,23 @@
         </is>
       </c>
       <c r="B49" s="17">
-        <f>Assumptions!$B$40</f>
+        <f>Assumptions!$B$41</f>
         <v/>
       </c>
       <c r="C49" s="17">
-        <f>Assumptions!$B$41</f>
+        <f>Assumptions!$B$42</f>
         <v/>
       </c>
       <c r="D49" s="17">
-        <f>Assumptions!$B$41</f>
+        <f>Assumptions!$B$42</f>
         <v/>
       </c>
       <c r="E49" s="17">
-        <f>Assumptions!$B$41</f>
+        <f>Assumptions!$B$42</f>
         <v/>
       </c>
       <c r="F49" s="17">
-        <f>Assumptions!$B$41</f>
+        <f>Assumptions!$B$42</f>
         <v/>
       </c>
     </row>
@@ -9235,23 +9339,23 @@
         </is>
       </c>
       <c r="B50" s="30">
-        <f>(B37*Assumptions!$B$37/365+(B38+B39)*Assumptions!$B$38/365-(B38+B39)*Assumptions!$B$39/365)-(5847.773*Assumptions!$B$37/365+3099*Assumptions!$B$38/365-3099*Assumptions!$B$39/365)</f>
+        <f>(B37*Assumptions!$B$38/365+(B38+B39)*Assumptions!$B$39/365-(B38+B39)*Assumptions!$B$40/365)-(5847.773*Assumptions!$B$38/365+3099*Assumptions!$B$39/365-3099*Assumptions!$B$40/365)</f>
         <v/>
       </c>
       <c r="C50" s="30">
-        <f>(C37*Assumptions!$B$37/365+(C38+C39)*Assumptions!$B$38/365-(C38+C39)*Assumptions!$B$39/365)-(B37*Assumptions!$B$37/365+(B38+B39)*Assumptions!$B$38/365-(B38+B39)*Assumptions!$B$39/365)</f>
+        <f>(C37*Assumptions!$B$38/365+(C38+C39)*Assumptions!$B$39/365-(C38+C39)*Assumptions!$B$40/365)-(B37*Assumptions!$B$38/365+(B38+B39)*Assumptions!$B$39/365-(B38+B39)*Assumptions!$B$40/365)</f>
         <v/>
       </c>
       <c r="D50" s="30">
-        <f>(D37*Assumptions!$B$37/365+(D38+D39)*Assumptions!$B$38/365-(D38+D39)*Assumptions!$B$39/365)-(C37*Assumptions!$B$37/365+(C38+C39)*Assumptions!$B$38/365-(C38+C39)*Assumptions!$B$39/365)</f>
+        <f>(D37*Assumptions!$B$38/365+(D38+D39)*Assumptions!$B$39/365-(D38+D39)*Assumptions!$B$40/365)-(C37*Assumptions!$B$38/365+(C38+C39)*Assumptions!$B$39/365-(C38+C39)*Assumptions!$B$40/365)</f>
         <v/>
       </c>
       <c r="E50" s="30">
-        <f>(E37*Assumptions!$B$37/365+(E38+E39)*Assumptions!$B$38/365-(E38+E39)*Assumptions!$B$39/365)-(D37*Assumptions!$B$37/365+(D38+D39)*Assumptions!$B$38/365-(D38+D39)*Assumptions!$B$39/365)</f>
+        <f>(E37*Assumptions!$B$38/365+(E38+E39)*Assumptions!$B$39/365-(E38+E39)*Assumptions!$B$40/365)-(D37*Assumptions!$B$38/365+(D38+D39)*Assumptions!$B$39/365-(D38+D39)*Assumptions!$B$40/365)</f>
         <v/>
       </c>
       <c r="F50" s="30">
-        <f>(F37*Assumptions!$B$37/365+(F38+F39)*Assumptions!$B$38/365-(F38+F39)*Assumptions!$B$39/365)-(E37*Assumptions!$B$37/365+(E38+E39)*Assumptions!$B$38/365-(E38+E39)*Assumptions!$B$39/365)</f>
+        <f>(F37*Assumptions!$B$38/365+(F38+F39)*Assumptions!$B$39/365-(F38+F39)*Assumptions!$B$40/365)-(E37*Assumptions!$B$38/365+(E38+E39)*Assumptions!$B$39/365-(E38+E39)*Assumptions!$B$40/365)</f>
         <v/>
       </c>
     </row>
@@ -9397,7 +9501,7 @@
         </is>
       </c>
       <c r="B58" s="17">
-        <f>B57*(1+Assumptions!$B$46)</f>
+        <f>B57*(1+Assumptions!$B$51)</f>
         <v/>
       </c>
     </row>
@@ -9408,7 +9512,7 @@
         </is>
       </c>
       <c r="B59" s="11">
-        <f>Assumptions!$B$46/Assumptions!$B$47</f>
+        <f>Assumptions!$B$51/Assumptions!$B$52</f>
         <v/>
       </c>
     </row>
@@ -9430,7 +9534,7 @@
         </is>
       </c>
       <c r="B61" s="17">
-        <f>B60/(F52-Assumptions!$B$46)</f>
+        <f>B60/(F52-Assumptions!$B$51)</f>
         <v/>
       </c>
     </row>
@@ -9522,11 +9626,11 @@
         </is>
       </c>
       <c r="B68" s="17">
-        <f>B33+2504.9806793283</f>
+        <f>B33+289.62532316473835</f>
         <v/>
       </c>
       <c r="C68" s="17">
-        <f>B68-Assumptions!$B$48-Assumptions!$B$49-Assumptions!$B$50</f>
+        <f>B68-Assumptions!$B$53-Assumptions!$B$54-Assumptions!$B$55</f>
         <v/>
       </c>
       <c r="D68" s="19">
@@ -9549,11 +9653,11 @@
         </is>
       </c>
       <c r="B69" s="18">
-        <f>15723.830918783875</f>
+        <f>15613.019549116816</f>
         <v/>
       </c>
       <c r="C69" s="17">
-        <f>B69-Assumptions!$B$48-Assumptions!$B$49-Assumptions!$B$50</f>
+        <f>B69-Assumptions!$B$53-Assumptions!$B$54-Assumptions!$B$55</f>
         <v/>
       </c>
       <c r="D69" s="19">
@@ -9561,7 +9665,7 @@
         <v/>
       </c>
       <c r="E69" s="9">
-        <f>0.5971655207990052</f>
+        <f>0.6595621515533581</f>
         <v/>
       </c>
       <c r="F69" s="21">
@@ -9576,11 +9680,11 @@
         </is>
       </c>
       <c r="B70" s="17">
-        <f>B64+2566.7801399883047</f>
+        <f>B64+227.7696594052444</f>
         <v/>
       </c>
       <c r="C70" s="17">
-        <f>B70-Assumptions!$B$48-Assumptions!$B$49-Assumptions!$B$50</f>
+        <f>B70-Assumptions!$B$53-Assumptions!$B$54-Assumptions!$B$55</f>
         <v/>
       </c>
       <c r="D70" s="19">
@@ -9603,11 +9707,11 @@
         </is>
       </c>
       <c r="B71" s="18">
-        <f>15772.12633626277</f>
+        <f>14246.549189859363</f>
         <v/>
       </c>
       <c r="C71" s="17">
-        <f>B71-Assumptions!$B$48-Assumptions!$B$49-Assumptions!$B$50</f>
+        <f>B71-Assumptions!$B$53-Assumptions!$B$54-Assumptions!$B$55</f>
         <v/>
       </c>
       <c r="D71" s="19">
@@ -9615,7 +9719,7 @@
         <v/>
       </c>
       <c r="E71" s="9">
-        <f>0.5890403753793205</f>
+        <f>0.7042011380077203</f>
         <v/>
       </c>
       <c r="F71" s="21">
@@ -10065,23 +10169,23 @@
         <v>154.219</v>
       </c>
       <c r="E14" s="30">
-        <f>Assumptions!$B$48*Assumptions!$B$18</f>
+        <f>Assumptions!$B$53*Assumptions!$B$18</f>
         <v/>
       </c>
       <c r="F14" s="30">
-        <f>Assumptions!$B$48*Assumptions!$B$18</f>
+        <f>Assumptions!$B$53*Assumptions!$B$18</f>
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>Assumptions!$B$48*Assumptions!$B$18</f>
+        <f>Assumptions!$B$53*Assumptions!$B$18</f>
         <v/>
       </c>
       <c r="H14" s="30">
-        <f>Assumptions!$B$48*Assumptions!$B$18</f>
+        <f>Assumptions!$B$53*Assumptions!$B$18</f>
         <v/>
       </c>
       <c r="I14" s="30">
-        <f>Assumptions!$B$48*Assumptions!$B$18</f>
+        <f>Assumptions!$B$53*Assumptions!$B$18</f>
         <v/>
       </c>
     </row>

--- a/engine/borouge_study/BOROUGE_Valuation_Model_09082026_public.xlsx
+++ b/engine/borouge_study/BOROUGE_Valuation_Model_09082026_public.xlsx
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="B19" s="22">
-        <f>Assumptions!$B$5*(1+0.05)</f>
+        <f>$B$5*(1+0.05)</f>
         <v/>
       </c>
       <c r="C19" s="28" t="n">
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="B20" s="22">
-        <f>Assumptions!$B$5*(1-0.05)</f>
+        <f>$B$5*(1-0.05)</f>
         <v/>
       </c>
       <c r="C20" s="28" t="n">
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B21" s="22">
-        <f>Assumptions!$B$5*(1+0.1)</f>
+        <f>$B$5*(1+0.1)</f>
         <v/>
       </c>
       <c r="C21" s="28" t="n">
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="B22" s="22">
-        <f>Assumptions!$B$5*(1-0.1)</f>
+        <f>$B$5*(1-0.1)</f>
         <v/>
       </c>
       <c r="C22" s="28" t="n">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="B23" s="22">
-        <f>Assumptions!$B$5*(1+0.15)</f>
+        <f>$B$5*(1+0.15)</f>
         <v/>
       </c>
       <c r="C23" s="28" t="n">
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="B24" s="22">
-        <f>Assumptions!$B$5*(1-0.15)</f>
+        <f>$B$5*(1-0.15)</f>
         <v/>
       </c>
       <c r="C24" s="28" t="n">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="B25" s="22">
-        <f>Assumptions!$B$5*(1+0.2)</f>
+        <f>$B$5*(1+0.2)</f>
         <v/>
       </c>
       <c r="C25" s="28" t="n">
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="B26" s="22">
-        <f>Assumptions!$B$5*(1-0.2)</f>
+        <f>$B$5*(1-0.2)</f>
         <v/>
       </c>
       <c r="C26" s="28" t="n">
@@ -2939,102 +2939,102 @@
     </row>
     <row r="6">
       <c r="A6" s="26" t="n">
-        <v>0.0508701898195711</v>
+        <v>0.05080556770080059</v>
       </c>
       <c r="B6" s="23" t="n">
-        <v>2.893894044153059</v>
+        <v>2.898960202547509</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>3.136632969508269</v>
+        <v>3.142789492812173</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>3.456448615077962</v>
+        <v>3.464210661588403</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>3.898031445496553</v>
+        <v>3.908325533070411</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>4.548899005574333</v>
+        <v>4.563591464781581</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="26" t="n">
-        <v>0.05587018981957111</v>
+        <v>0.0558055677008006</v>
       </c>
       <c r="B7" s="23" t="n">
-        <v>2.544997614368152</v>
+        <v>2.549023446208399</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>2.719048021800045</v>
+        <v>2.723795618614905</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>2.940313511870105</v>
+        <v>2.946069265900841</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>3.231736160532899</v>
+        <v>3.238974042098614</v>
       </c>
       <c r="F7" s="23" t="n">
-        <v>3.633994346502716</v>
+        <v>3.643565697113109</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="26" t="n">
-        <v>0.0608701898195711</v>
+        <v>0.0608055677008006</v>
       </c>
       <c r="B8" s="23" t="n">
-        <v>2.264351045241041</v>
+        <v>2.267627983906301</v>
       </c>
       <c r="C8" s="23" t="n">
-        <v>2.392041742172137</v>
+        <v>2.395815594658295</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>2.549854919607749</v>
+        <v>2.554294823769648</v>
       </c>
       <c r="E8" s="23" t="n">
-        <v>2.750387031869435</v>
+        <v>2.755755716520112</v>
       </c>
       <c r="F8" s="23" t="n">
-        <v>3.014395451235635</v>
+        <v>3.021127118008359</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="26" t="n">
-        <v>0.0658701898195711</v>
+        <v>0.06580556770080059</v>
       </c>
       <c r="B9" s="23" t="n">
-        <v>2.033640537639993</v>
+        <v>2.03636047970787</v>
       </c>
       <c r="C9" s="23" t="n">
-        <v>2.128918623131629</v>
+        <v>2.131991479971111</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>2.243992778539845</v>
+        <v>2.247523228457307</v>
       </c>
       <c r="E9" s="23" t="n">
-        <v>2.386128471680169</v>
+        <v>2.390271178428454</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>2.566642148549217</v>
+        <v>2.571636993047264</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="26" t="n">
-        <v>0.07087018981957111</v>
+        <v>0.0708055677008006</v>
       </c>
       <c r="B10" s="23" t="n">
-        <v>1.840569286563959</v>
+        <v>1.842863725656926</v>
       </c>
       <c r="C10" s="23" t="n">
-        <v>1.912538974720122</v>
+        <v>1.915090430461655</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>1.997797390198996</v>
+        <v>2.000673093907594</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>2.100690076601443</v>
+        <v>2.10398540656718</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>2.22768908764244</v>
+        <v>2.231544732447075</v>
       </c>
     </row>
     <row r="12">
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="B14" s="23" t="n">
-        <v>1.61065079748036</v>
+        <v>1.61365215581326</v>
       </c>
       <c r="C14" s="23" t="n">
-        <v>1.425572526617797</v>
+        <v>1.428449833213424</v>
       </c>
     </row>
     <row r="15">
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="B15" s="23" t="n">
-        <v>2.080252858544056</v>
+        <v>2.083973489791456</v>
       </c>
       <c r="C15" s="23" t="n">
-        <v>1.886828798766677</v>
+        <v>1.890420574087241</v>
       </c>
     </row>
     <row r="16">
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="B16" s="23" t="n">
-        <v>2.549854919607749</v>
+        <v>2.554294823769648</v>
       </c>
       <c r="C16" s="23" t="n">
-        <v>2.348085070915562</v>
+        <v>2.35239131496106</v>
       </c>
     </row>
     <row r="17">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="B17" s="23" t="n">
-        <v>3.019456980671444</v>
+        <v>3.024616157747842</v>
       </c>
       <c r="C17" s="23" t="n">
-        <v>2.809341343064444</v>
+        <v>2.814362055834877</v>
       </c>
     </row>
     <row r="18">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="B18" s="23" t="n">
-        <v>3.48905904173514</v>
+        <v>3.494937491726039</v>
       </c>
       <c r="C18" s="23" t="n">
-        <v>3.270597615213326</v>
+        <v>3.276332796708694</v>
       </c>
     </row>
     <row r="20">
@@ -3175,10 +3175,10 @@
         </is>
       </c>
       <c r="B22" s="23" t="n">
-        <v>2.026691391607796</v>
+        <v>2.030336827905816</v>
       </c>
       <c r="C22" s="23" t="n">
-        <v>1.836039314234161</v>
+        <v>1.839558814625347</v>
       </c>
     </row>
     <row r="23">
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="B23" s="23" t="n">
-        <v>2.288273155607775</v>
+        <v>2.292315825837734</v>
       </c>
       <c r="C23" s="23" t="n">
-        <v>2.09206219257486</v>
+        <v>2.095975064793202</v>
       </c>
     </row>
     <row r="24">
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="B24" s="23" t="n">
-        <v>2.549854919607749</v>
+        <v>2.554294823769648</v>
       </c>
       <c r="C24" s="23" t="n">
-        <v>2.348085070915562</v>
+        <v>2.35239131496106</v>
       </c>
     </row>
     <row r="25">
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="B25" s="23" t="n">
-        <v>2.811436683607727</v>
+        <v>2.816273821701564</v>
       </c>
       <c r="C25" s="23" t="n">
-        <v>2.604107949256261</v>
+        <v>2.608807565128914</v>
       </c>
     </row>
     <row r="26">
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="B26" s="23" t="n">
-        <v>3.073018447607703</v>
+        <v>3.078252819633481</v>
       </c>
       <c r="C26" s="23" t="n">
-        <v>2.86013082759696</v>
+        <v>2.865223815296769</v>
       </c>
     </row>
     <row r="28">
@@ -4224,7 +4224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4384,7 +4384,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>THE FIELD AGAINST THE MARKET</t>
+          <t>THE ANSWER AGAINST THE MARKET</t>
         </is>
       </c>
       <c r="B12" s="5" t="n"/>
@@ -4398,12 +4398,12 @@
       <c r="J12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Lowest lens reading</t>
-        </is>
-      </c>
-      <c r="B13" s="8">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Navigation normalises during 2026</t>
+        </is>
+      </c>
+      <c r="B13" s="10">
         <f>'Fundamental Valuation'!$B$44</f>
         <v/>
       </c>
@@ -4411,7 +4411,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Median lens reading</t>
+          <t>Disruption persists into 2027</t>
         </is>
       </c>
       <c r="B14" s="10">
@@ -4422,198 +4422,213 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Highest lens reading</t>
+          <t>Closing price, 3 September 2026</t>
         </is>
       </c>
       <c r="B15" s="8">
-        <f>'Fundamental Valuation'!$B$46</f>
+        <f>Assumptions!$B$5</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Closing price, 7 August 2026</t>
-        </is>
-      </c>
-      <c r="B16" s="8">
-        <f>Assumptions!$B$5</f>
+          <t>Navigation normalises, against the close</t>
+        </is>
+      </c>
+      <c r="B16" s="11">
+        <f>B13/B15-1</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Median lens reading against the close</t>
+          <t>Disruption persists, against the close</t>
         </is>
       </c>
       <c r="B17" s="11">
-        <f>B14/B16-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+        <f>B14/B15-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Cross-checks span (AED)</t>
+        </is>
+      </c>
+      <c r="B18" s="8">
+        <f>'Fundamental Valuation'!$B$52</f>
+        <v/>
+      </c>
+      <c r="C18" s="8">
+        <f>'Fundamental Valuation'!$B$53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>THE COST OF CAPITAL BEHIND IT</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Weighted average cost of capital — own-stock beta</t>
-        </is>
-      </c>
-      <c r="B20" s="12">
-        <f>'Fundamental Valuation'!$B$29</f>
-        <v/>
-      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Weighted average cost of capital — sector bottom-up beta</t>
+          <t>Weighted average cost of capital — own-stock beta</t>
         </is>
       </c>
       <c r="B21" s="12">
-        <f>'Fundamental Valuation'!$C$29</f>
+        <f>'Fundamental Valuation'!$B$29</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Normalised risk-free rate</t>
+          <t>Weighted average cost of capital — sector bottom-up beta</t>
         </is>
       </c>
       <c r="B22" s="12">
-        <f>'Fundamental Valuation'!$B$7</f>
+        <f>'Fundamental Valuation'!$C$29</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Equity risk premium (rating basis)</t>
+          <t>Normalised risk-free rate</t>
         </is>
       </c>
       <c r="B23" s="12">
-        <f>'Fundamental Valuation'!$B$12</f>
+        <f>'Fundamental Valuation'!$B$7</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
+          <t>Equity risk premium (rating basis)</t>
+        </is>
+      </c>
+      <c r="B24" s="12">
+        <f>'Fundamental Valuation'!$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
           <t>Terminal growth rate</t>
         </is>
       </c>
-      <c r="B24" s="12">
+      <c r="B25" s="12">
         <f>Assumptions!$B$51</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>THE PROBABILITY MAP FOR THE TRADED PRICE</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>Horizon</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>5th</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Median</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>95th</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>Above the close</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>One month</t>
-        </is>
-      </c>
-      <c r="B28" s="8">
-        <f>'Monte Carlo'!C14</f>
-        <v/>
-      </c>
-      <c r="C28" s="8">
-        <f>'Monte Carlo'!E14</f>
-        <v/>
-      </c>
-      <c r="D28" s="8">
-        <f>'Monte Carlo'!G14</f>
-        <v/>
-      </c>
-      <c r="E28" s="9">
-        <f>'Monte Carlo'!H14</f>
-        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
+          <t>One month</t>
+        </is>
+      </c>
+      <c r="B29" s="8">
+        <f>'Monte Carlo'!C14</f>
+        <v/>
+      </c>
+      <c r="C29" s="8">
+        <f>'Monte Carlo'!E14</f>
+        <v/>
+      </c>
+      <c r="D29" s="8">
+        <f>'Monte Carlo'!G14</f>
+        <v/>
+      </c>
+      <c r="E29" s="9">
+        <f>'Monte Carlo'!H14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
           <t>Three months</t>
         </is>
       </c>
-      <c r="B29" s="8">
+      <c r="B30" s="8">
         <f>'Monte Carlo'!C15</f>
         <v/>
       </c>
-      <c r="C29" s="8">
+      <c r="C30" s="8">
         <f>'Monte Carlo'!E15</f>
         <v/>
       </c>
-      <c r="D29" s="8">
+      <c r="D30" s="8">
         <f>'Monte Carlo'!G15</f>
         <v/>
       </c>
-      <c r="E29" s="9">
+      <c r="E30" s="9">
         <f>'Monte Carlo'!H15</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>The two constructions and the two betas are shown side by side and are never averaged. The spread between them is the honest width of the answer.</t>
         </is>
@@ -4621,7 +4636,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A32:I32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4633,7 +4648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -5130,7 +5145,7 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>THE FIELD</t>
+          <t>THE ANSWER — the cash-flow lens, both sides of the shipping-lane judgement</t>
         </is>
       </c>
       <c r="B43" s="5" t="n"/>
@@ -5144,42 +5159,42 @@
       <c r="J43" s="5" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Lowest lens reading (AED)</t>
-        </is>
-      </c>
-      <c r="B44" s="22">
-        <f>MIN(B34,B35,B39,B40,B41,C34,C35,C39,C40)</f>
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Navigation normalises during 2026 (AED)</t>
+        </is>
+      </c>
+      <c r="B44" s="21">
+        <f>C34</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Median lens reading (AED)</t>
+          <t>Disruption persists into 2027 (AED)</t>
         </is>
       </c>
       <c r="B45" s="21">
-        <f>MEDIAN(B34,B35,B39,B40,B41,C34,C35,C39,C40)</f>
+        <f>C35</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Highest lens reading (AED)</t>
+          <t>The judgement is worth (AED a share)</t>
         </is>
       </c>
       <c r="B46" s="22">
-        <f>MAX(B34,B35,B39,B40,B41,C34,C35,C39,C40)</f>
+        <f>$B$44-$B$45</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Closing price, 7 August 2026 (AED)</t>
+          <t>Closing price, 3 September 2026 (AED)</t>
         </is>
       </c>
       <c r="B47" s="8">
@@ -5190,11 +5205,71 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Median lens reading against the close</t>
+          <t>Navigation normalises, against the close</t>
         </is>
       </c>
       <c r="B48" s="11">
-        <f>$B$45/B47-1</f>
+        <f>$B$44/$B$47-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Disruption persists, against the close</t>
+        </is>
+      </c>
+      <c r="B49" s="11">
+        <f>$B$45/$B$47-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>THE FIELD OF CROSS-CHECKS — published beside the answer, never averaged into it</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Lowest lens reading (AED)</t>
+        </is>
+      </c>
+      <c r="B52" s="22">
+        <f>MIN(B34,B35,B39,B40,B41,C34,C35,C39,C40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Highest lens reading (AED)</t>
+        </is>
+      </c>
+      <c r="B53" s="22">
+        <f>MAX(B34,B35,B39,B40,B41,C34,C35,C39,C40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>RETIRED — the median of the nine readings, published unused (AED)</t>
+        </is>
+      </c>
+      <c r="B54" s="22">
+        <f>MEDIAN(B34,B35,B39,B40,B41,C34,C35,C39,C40)</f>
         <v/>
       </c>
     </row>
@@ -5271,7 +5346,7 @@
         </is>
       </c>
       <c r="B5" s="23" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -5432,7 +5507,7 @@
         </is>
       </c>
       <c r="B17" s="28" t="n">
-        <v>0.1667271180099881</v>
+        <v>0.1702745034995623</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -9626,7 +9701,7 @@
         </is>
       </c>
       <c r="B68" s="17">
-        <f>B33+289.62532316473835</f>
+        <f>B33+289.69167627572995</f>
         <v/>
       </c>
       <c r="C68" s="17">
@@ -9653,7 +9728,7 @@
         </is>
       </c>
       <c r="B69" s="18">
-        <f>15613.019549116816</f>
+        <f>15622.840225974325</f>
         <v/>
       </c>
       <c r="C69" s="17">
@@ -9665,7 +9740,7 @@
         <v/>
       </c>
       <c r="E69" s="9">
-        <f>0.6595621515533581</f>
+        <f>0.6597358609617034</f>
         <v/>
       </c>
       <c r="F69" s="21">
@@ -9680,7 +9755,7 @@
         </is>
       </c>
       <c r="B70" s="17">
-        <f>B64+227.7696594052444</f>
+        <f>B64+227.82184139446377</f>
         <v/>
       </c>
       <c r="C70" s="17">
@@ -9707,7 +9782,7 @@
         </is>
       </c>
       <c r="B71" s="18">
-        <f>14246.549189859363</f>
+        <f>14256.01620520997</f>
         <v/>
       </c>
       <c r="C71" s="17">
@@ -9719,7 +9794,7 @@
         <v/>
       </c>
       <c r="E71" s="9">
-        <f>0.7042011380077203</f>
+        <f>0.7043616097878573</f>
         <v/>
       </c>
       <c r="F71" s="21">
